--- a/Firm_Budget_Forecast_2026.xlsx
+++ b/Firm_Budget_Forecast_2026.xlsx
@@ -14,11 +14,13 @@
     <sheet name="Monthly Capacity" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Budget P&amp;L" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Budget vs Actual" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Guide" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Forecast 2026" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Guide" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Budget P&amp;L'!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'Budget vs Actual'!$A:$A</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Titles" vbProcedure="false">'Forecast 2026'!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Monthly Capacity'!$A:$A</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Staff P&amp;L'!$A:$A</definedName>
   </definedNames>
@@ -339,7 +341,31 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Set to the number of months of actuals entered above (7 = through July).</t>
+          <t xml:space="preserve">Number of months of actuals entered above (7 = through July).
+The Forecast tab uses actuals for these months and budget thereafter.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Mirror of Assumptions!B15. Utilization only moves BUDGET months — actual months are historical fact.
+Set it to 91% to carry the YTD run-rate forward.</t>
         </r>
       </text>
     </comment>
@@ -348,7 +374,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="411">
   <si>
     <t xml:space="preserve">Onyx Accounting Group, LLC</t>
   </si>
@@ -1215,19 +1241,19 @@
     <t xml:space="preserve">Budget vs Actual — 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Actuals are yellow inputs — paste each month from QuickBooks. Budget is live from the Budget P&amp;L tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ The Jan–Jul actuals loaded here are CASH BASIS (per the QuickBooks footer). The budget is accrual. See the reconciliation at the bottom.</t>
+    <t xml:space="preserve">Actuals are yellow inputs — paste each month from QuickBooks, then raise the month counter in B6. Budget is live from the Budget P&amp;L tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actuals are CASH BASIS, per the QuickBooks footer. The budget is accrual — see the reconciliation at the bottom before comparing revenue.</t>
   </si>
   <si>
     <t xml:space="preserve">Months of actuals entered</t>
   </si>
   <si>
-    <t xml:space="preserve">← YTD columns compare budget and actual through this month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTUALS  (from QuickBooks)</t>
+    <t xml:space="preserve">← drives the YTD columns AND the actual/budget cut-over on the Forecast tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTUALS  (from QuickBooks, cash basis)</t>
   </si>
   <si>
     <t xml:space="preserve">YTD</t>
@@ -1251,10 +1277,22 @@
     <t xml:space="preserve">    Wages</t>
   </si>
   <si>
+    <t xml:space="preserve">    Benefits - PEO</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total COGS</t>
   </si>
   <si>
-    <t xml:space="preserve">    Total Operating Expenses</t>
+    <t xml:space="preserve">Operating Expenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    PTO-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Unapplied Cash Bill Payment Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Operating Expenses</t>
   </si>
   <si>
     <t xml:space="preserve">NET INCOME  (actual)</t>
@@ -1275,15 +1313,18 @@
     <t xml:space="preserve">Var %</t>
   </si>
   <si>
-    <t xml:space="preserve">Variance shown favourable-positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Operating Expenses</t>
+    <t xml:space="preserve">variance shown favourable-positive</t>
   </si>
   <si>
     <t xml:space="preserve">NET INCOME</t>
   </si>
   <si>
+    <t xml:space="preserve">Implied utilization from YTD actuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← actual revenue ÷ modelled capacity. Set Assumptions!B15 to this to match reality.</t>
+  </si>
+  <si>
     <t xml:space="preserve">WHY ACTUAL NET INCOME LOOKS HIGHER THAN BUDGET</t>
   </si>
   <si>
@@ -1305,7 +1346,7 @@
     <t xml:space="preserve">    Admin salary not in operating expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Budget carries Josephine's admin share in OpEx. Actual OpEx has no salary line — payroll is posted entirely to COGS Wages.</t>
+    <t xml:space="preserve">Budget carries Josephine's admin share in OpEx. Actual OpEx has no salary line — payroll posts entirely to COGS Wages.</t>
   </si>
   <si>
     <t xml:space="preserve">    Admin payroll taxes</t>
@@ -1326,67 +1367,175 @@
     <t xml:space="preserve">Subtotal — budgeted costs absent from the actual P&amp;L</t>
   </si>
   <si>
-    <t xml:space="preserve">This is the bulk of the apparent out-performance — it is a scope difference, not profit.</t>
+    <t xml:space="preserve">This is the bulk of the apparent out-performance — a scope difference, not profit.</t>
   </si>
   <si>
     <t xml:space="preserve">Also affecting comparability</t>
   </si>
   <si>
-    <t xml:space="preserve">• Basis mismatch — the loaded actuals are CASH basis; the budget is accrual. For Jan–Jun, accrual sales were $555,286 vs $513,649 cash, so accrual revenue runs roughly $42k higher over that stretch.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Staffing ramp — actual wages climb from $18,160 in January to $91,281 in July. The budget assumes the full six-person team from 1 January, so early-month actual costs are far lower than budget.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• July is an outlier on both sides: revenue $177,148 against a ~$103k trend, and wages $91,281. Strip the one-time items before drawing a run-rate conclusion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Revenue is running BELOW capacity: $692,433 actual vs $763,218 budget for Jan–Jul, i.e. about 91% of modelled billable capacity. Dial Assumptions!B15 (utilization) to about 91% to match reality.</t>
+    <t xml:space="preserve">• Basis mismatch — actuals are CASH basis, the budget accrual. For Jan–Jun, accrual sales were $555,286 against $513,649 cash, so accrual revenue runs roughly $42k higher over that stretch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Staffing ramp — actual wages climb from $18,160 in January to $91,281 in July. The budget assumes the full six-person team from 1 January.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• July is an outlier on both sides: revenue $177,148 against a ~$103k trend, and wages $91,281. Strip one-time items before drawing a run-rate conclusion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast 2026 — Actual to date + Budget for the balance of the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each month pulls ACTUAL if it is on or before the cut-over month, otherwise BUDGET. Raise the counter on Budget vs Actual!B6 as each month closes and this tab re-blends itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut-over: months of actuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← actual through this month; budget after. Change it on the Budget vs Actual tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization (budget months only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← left: live setting (edit on Assumptions!B15).  right: implied by YTD actuals — set the toggle to this to carry actual run-rate forward.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLENDED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INCOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COST OF GOODS SOLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Cost of Goods Sold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROSS PROFIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO-FORMA — full-year economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The actual months carry no owner compensation, admin salary or benefits, because those are not on the QuickBooks P&amp;L. This block restates the full year as if every month bore them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net income as forecast above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: owner compensation for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: admin salary for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: admin payroll taxes for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: admin PEO benefits for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: COGS PEO benefits for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Less: IT for the actual months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRO-FORMA NET INCOME  (all costs expensed all year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Green ACTUAL months are historical fact — the utilization toggle does not move them. It only re-prices the amber BUDGET months.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Actuals are cash basis; the budget is accrual. Revenue timing is therefore not strictly comparable month to month, though the full-year total converges as receivables settle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• To roll forward: paste the new month's QuickBooks column into the Budget vs Actual tab, then raise Budget vs Actual!B6 by one. Nothing else needs touching.</t>
   </si>
   <si>
     <t xml:space="preserve">Firm Budget &amp; Forecast — 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Updated 2026-08-07  •  Revenue and hourly wages are driven by the real 2026 working-day calendar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOW THIS WORKBOOK WORKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 1 — Bill Rates</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 bill rate per client for CFO / Controller / Staff. The blended average of the 42 priced clients ($250.00 / $153.21 / $96.31) drives the model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 2 — Assumptions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Every lever: hours, PTO, utilization, employer tax rates, owner comp, benefits. The flat 'hours per week × 4' block is legacy — Monthly Capacity is the live driver.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 3 — Staff P&amp;L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pay + full labor burden (AZ/US employer tax + PEO benefits) → loaded cost per hour, and gross profit per person. Hours and revenue come from Monthly Capacity.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 4 — Monthly Capacity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW. Real 2026 calendar: weekdays − company holidays = working days → billable hours per person per month → revenue. Also drives hourly-staff wage cost.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 5 — Budget P&amp;L (QBO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monthly P&amp;L in QuickBooks layout. Revenue and hourly wages vary by month with working days; salaries, taxes and benefits are annual ÷ 12.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tab 6 — Budget vs Actual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEW. Paste QuickBooks actuals each month. YTD budget-vs-actual plus a reconciliation of why actual net income reads higher than budget.</t>
+    <t xml:space="preserve">Updated 2026-08-07  •  Actuals through July blended with budget for the balance of 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">START HERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headline tab: actual months to date + budget for the rest of the year, in QuickBooks layout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly roll-forward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste the new month's QuickBooks column into Budget vs Actual, then raise the month counter in Budget vs Actual!B6 by one. Everything re-blends automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization toggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions!B15. Affects BUDGET months only — actual months are historical fact. YTD actuals imply about 91%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE TABS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bill Rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 bill rate per client. The blended average of the 42 priced clients ($250.00 / $153.21 / $96.31) drives the model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every lever: hours, PTO, utilization, employer tax rates, owner comp. The flat 'hours × 4 weeks' block is legacy and feeds nothing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Staff P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pay + full labor burden (AZ/US employer tax + PEO benefits) → loaded cost per hour and gross profit per person.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Monthly Capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real 2026 calendar: weekdays − holidays = working days → billable hours per person per month → revenue. Also drives hourly wage cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Budget P&amp;L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pure budget, all 12 months, at the utilization you set. This is the 'full capacity' plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Budget vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where actuals live. Paste QuickBooks here. YTD variance and the reconciliation of the net income gap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. Forecast 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual + budget blended. Includes a pro-forma restating the year as if owner comp and benefits were expensed throughout.</t>
   </si>
   <si>
     <t xml:space="preserve">COLOR LEGEND</t>
@@ -1410,7 +1559,19 @@
     <t xml:space="preserve">Calculated formula — do not type over</t>
   </si>
   <si>
-    <t xml:space="preserve">KEY OUTPUTS (2026 full year, at 100% utilization)</t>
+    <t xml:space="preserve">ACTUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast month sourced from QuickBooks actuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUDGET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast month sourced from the budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KEY OUTPUTS — FORECAST 2026  (actual to July + budget after)</t>
   </si>
   <si>
     <t xml:space="preserve">Total revenue</t>
@@ -1419,22 +1580,22 @@
     <t xml:space="preserve">Gross profit</t>
   </si>
   <si>
-    <t xml:space="preserve">Gross margin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total operating expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Net income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net margin</t>
+    <t xml:space="preserve">NET INCOME (as reported basis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma net income (all costs expensed)</t>
   </si>
   <si>
     <t xml:space="preserve">Owner salary (Steven, = SS max)</t>
   </si>
   <si>
-    <t xml:space="preserve">Billable hours available (all staff)</t>
+    <t xml:space="preserve">Utilization setting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilization implied by YTD actuals</t>
   </si>
   <si>
     <t xml:space="preserve">Working days in 2026</t>
@@ -1446,19 +1607,19 @@
     <t xml:space="preserve">•</t>
   </si>
   <si>
+    <t xml:space="preserve">Actuals: Onyx Accounting Group LLC Profit and Loss, Jan–Jul 2026 — CASH BASIS per the QuickBooks footer. The budget is accrual; switch the actuals to accrual when you are ready.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The actual months carry no owner compensation, admin salary, PEO benefits or IT, because those are not on the QuickBooks P&amp;L. The pro-forma block on Forecast 2026 restates the year with them.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bill rates: Clients Billing Rates Master Sheet 2026 — blended average of the 42 priced clients.</t>
   </si>
   <si>
-    <t xml:space="preserve">Salaries / pay: Cost Sheet.xlsx. Steven $184,500 = 2026 Social Security wage-base max.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valentina: contractor at $4,200/mo (Bulgaria) — no US payroll tax or PEO benefits.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTO: 80 hrs/yr (2 weeks) — Onyx Handbook, 'Paid Time Off'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holidays: 7 paid days — Onyx Handbook. Excluded from working days on the Monthly Capacity tab, so they are never deducted twice.</t>
+    <t xml:space="preserve">Salaries / pay: Cost Sheet.xlsx. Steven $184,500 = 2026 Social Security wage-base max. Valentina is a $4,200/mo Bulgaria contractor — no US payroll tax or PEO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTO 80 hrs/yr and 7 paid holidays — Onyx Handbook. Holidays are excluded once, on Monthly Capacity, so they are never deducted twice.</t>
   </si>
   <si>
     <t xml:space="preserve">2026 calendar: 261 weekdays, 7 holidays, 254 working days = 2,032 working hrs and 2,088 paid hrs per FTE.</t>
@@ -1467,17 +1628,14 @@
     <t xml:space="preserve">Benefits: $800/mo per employee placeholder on Staff P&amp;L — replace with the PEO quote for insurance + 401(k).</t>
   </si>
   <si>
-    <t xml:space="preserve">OpEx defaults are H1-2026 monthly averages from the QBO P&amp;L (the one-time $30k reimbursement excluded).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilization (Assumptions!B15) is set to 100%. Jan–Jul actuals imply roughly 91% — dial it down for a realistic forecast.</t>
+    <t xml:space="preserve">Budget-month OpEx defaults are H1-2026 monthly averages (the one-time $30k reimbursement excluded). Review before relying on the Aug–Dec figures.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="General"/>
@@ -1487,8 +1645,9 @@
     <numFmt numFmtId="170" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="171" formatCode="0.00%"/>
     <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="173" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1718,6 +1877,46 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="16"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
@@ -1727,7 +1926,15 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF375623"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF7F6000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1740,7 +1947,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1750,13 +1957,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
+        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1780,7 +1987,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1853,7 +2072,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="141">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2234,6 +2453,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2270,6 +2493,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2290,7 +2517,67 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="19" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="31" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="34" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2298,23 +2585,39 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2330,7 +2633,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2343,6 +2646,38 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF375623"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FF7F6000"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2356,15 +2691,15 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF7F6000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -2378,8 +2713,8 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -2400,7 +2735,7 @@
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="FF375623"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -8396,7 +8731,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
@@ -8483,37 +8818,50 @@
       <c r="A9" s="94" t="s">
         <v>227</v>
       </c>
+      <c r="B9" s="95"/>
+      <c r="C9" s="95"/>
+      <c r="D9" s="95"/>
+      <c r="E9" s="95"/>
+      <c r="F9" s="95"/>
+      <c r="G9" s="95"/>
+      <c r="H9" s="95"/>
+      <c r="I9" s="95"/>
+      <c r="J9" s="95"/>
+      <c r="K9" s="95"/>
+      <c r="L9" s="95"/>
+      <c r="M9" s="95"/>
+      <c r="N9" s="95"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="B10" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="95" t="n">
+      <c r="B10" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="96" t="n">
         <v>46.75</v>
       </c>
-      <c r="D10" s="95" t="n">
+      <c r="D10" s="96" t="n">
         <v>21</v>
       </c>
-      <c r="E10" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="95" t="n">
+      <c r="E10" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="96" t="n">
         <v>2294</v>
       </c>
-      <c r="G10" s="95" t="n">
+      <c r="G10" s="96" t="n">
         <v>-418</v>
       </c>
-      <c r="H10" s="95" t="n">
+      <c r="H10" s="96" t="n">
         <v>-152.69</v>
       </c>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="95"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
       <c r="N10" s="75" t="n">
         <f aca="false">SUM(B10:M10)</f>
         <v>1791.06</v>
@@ -8523,32 +8871,32 @@
       <c r="A11" s="54" t="s">
         <v>230</v>
       </c>
-      <c r="B11" s="95" t="n">
+      <c r="B11" s="96" t="n">
         <v>64981.75</v>
       </c>
-      <c r="C11" s="95" t="n">
+      <c r="C11" s="96" t="n">
         <v>55772</v>
       </c>
-      <c r="D11" s="95" t="n">
+      <c r="D11" s="96" t="n">
         <v>103377.75</v>
       </c>
-      <c r="E11" s="95" t="n">
+      <c r="E11" s="96" t="n">
         <v>88464.25</v>
       </c>
-      <c r="F11" s="95" t="n">
+      <c r="F11" s="96" t="n">
         <v>97011.45</v>
       </c>
-      <c r="G11" s="95" t="n">
+      <c r="G11" s="96" t="n">
         <v>104042</v>
       </c>
-      <c r="H11" s="95" t="n">
+      <c r="H11" s="96" t="n">
         <v>177147.55</v>
       </c>
-      <c r="I11" s="95"/>
-      <c r="J11" s="95"/>
-      <c r="K11" s="95"/>
-      <c r="L11" s="95"/>
-      <c r="M11" s="95"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
       <c r="N11" s="75" t="n">
         <f aca="false">SUM(B11:M11)</f>
         <v>690796.75</v>
@@ -8558,39 +8906,39 @@
       <c r="A12" s="54" t="s">
         <v>287</v>
       </c>
-      <c r="B12" s="95" t="n">
+      <c r="B12" s="96" t="n">
         <v>-154.75</v>
       </c>
-      <c r="C12" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="95" t="n">
+      <c r="C12" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="96" t="n">
         <v>1000</v>
       </c>
-      <c r="F12" s="95" t="n">
+      <c r="F12" s="96" t="n">
         <v>875</v>
       </c>
-      <c r="G12" s="95" t="n">
+      <c r="G12" s="96" t="n">
         <v>-1500</v>
       </c>
-      <c r="H12" s="95" t="n">
+      <c r="H12" s="96" t="n">
         <v>-375</v>
       </c>
-      <c r="I12" s="95"/>
-      <c r="J12" s="95"/>
-      <c r="K12" s="95"/>
-      <c r="L12" s="95"/>
-      <c r="M12" s="95"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="96"/>
       <c r="N12" s="75" t="n">
         <f aca="false">SUM(B12:M12)</f>
         <v>-154.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="97" t="s">
         <v>288</v>
       </c>
       <c r="B13" s="75" t="n">
@@ -8650,37 +8998,50 @@
       <c r="A14" s="94" t="s">
         <v>233</v>
       </c>
+      <c r="B14" s="95"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="95"/>
+      <c r="I14" s="95"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="54" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="95" t="n">
+      <c r="B15" s="96" t="n">
         <v>1498.5</v>
       </c>
-      <c r="C15" s="95" t="n">
+      <c r="C15" s="96" t="n">
         <v>430</v>
       </c>
-      <c r="D15" s="95" t="n">
+      <c r="D15" s="96" t="n">
         <v>355.5</v>
       </c>
-      <c r="E15" s="95" t="n">
+      <c r="E15" s="96" t="n">
         <v>1089.5</v>
       </c>
-      <c r="F15" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="95"/>
-      <c r="J15" s="95"/>
-      <c r="K15" s="95"/>
-      <c r="L15" s="95"/>
-      <c r="M15" s="95"/>
+      <c r="F15" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
       <c r="N15" s="75" t="n">
         <f aca="false">SUM(B15:M15)</f>
         <v>3373.5</v>
@@ -8690,32 +9051,32 @@
       <c r="A16" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="B16" s="95" t="n">
+      <c r="B16" s="96" t="n">
         <v>94.5</v>
       </c>
-      <c r="C16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="95" t="n">
+      <c r="C16" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="96" t="n">
         <v>13.2</v>
       </c>
-      <c r="E16" s="95" t="n">
+      <c r="E16" s="96" t="n">
         <v>63.2</v>
       </c>
-      <c r="F16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="95"/>
-      <c r="J16" s="95"/>
-      <c r="K16" s="95"/>
-      <c r="L16" s="95"/>
-      <c r="M16" s="95"/>
+      <c r="F16" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="96"/>
+      <c r="J16" s="96"/>
+      <c r="K16" s="96"/>
+      <c r="L16" s="96"/>
+      <c r="M16" s="96"/>
       <c r="N16" s="75" t="n">
         <f aca="false">SUM(B16:M16)</f>
         <v>170.9</v>
@@ -8725,32 +9086,32 @@
       <c r="A17" s="54" t="s">
         <v>289</v>
       </c>
-      <c r="B17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="95" t="n">
+      <c r="B17" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="96" t="n">
         <v>435</v>
       </c>
-      <c r="D17" s="95" t="n">
+      <c r="D17" s="96" t="n">
         <v>435</v>
       </c>
-      <c r="E17" s="95" t="n">
+      <c r="E17" s="96" t="n">
         <v>435</v>
       </c>
-      <c r="F17" s="95" t="n">
+      <c r="F17" s="96" t="n">
         <v>870</v>
       </c>
-      <c r="G17" s="95" t="n">
+      <c r="G17" s="96" t="n">
         <v>435</v>
       </c>
-      <c r="H17" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="95"/>
-      <c r="J17" s="95"/>
-      <c r="K17" s="95"/>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
+      <c r="H17" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="96"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="96"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
       <c r="N17" s="75" t="n">
         <f aca="false">SUM(B17:M17)</f>
         <v>2610</v>
@@ -8760,32 +9121,32 @@
       <c r="A18" s="54" t="s">
         <v>290</v>
       </c>
-      <c r="B18" s="95" t="n">
+      <c r="B18" s="96" t="n">
         <v>4320</v>
       </c>
-      <c r="C18" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="95" t="n">
+      <c r="C18" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="96" t="n">
         <v>280</v>
       </c>
-      <c r="G18" s="95" t="n">
+      <c r="G18" s="96" t="n">
         <v>760</v>
       </c>
-      <c r="H18" s="95" t="n">
+      <c r="H18" s="96" t="n">
         <v>760</v>
       </c>
-      <c r="I18" s="95"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="95"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="96"/>
+      <c r="M18" s="96"/>
       <c r="N18" s="75" t="n">
         <f aca="false">SUM(B18:M18)</f>
         <v>6120</v>
@@ -8795,32 +9156,32 @@
       <c r="A19" s="54" t="s">
         <v>291</v>
       </c>
-      <c r="B19" s="95" t="n">
+      <c r="B19" s="96" t="n">
         <v>2271.72</v>
       </c>
-      <c r="C19" s="95" t="n">
+      <c r="C19" s="96" t="n">
         <v>2808.37</v>
       </c>
-      <c r="D19" s="95" t="n">
+      <c r="D19" s="96" t="n">
         <v>2893.57</v>
       </c>
-      <c r="E19" s="95" t="n">
+      <c r="E19" s="96" t="n">
         <v>2750.47</v>
       </c>
-      <c r="F19" s="95" t="n">
+      <c r="F19" s="96" t="n">
         <v>3979.19</v>
       </c>
-      <c r="G19" s="95" t="n">
+      <c r="G19" s="96" t="n">
         <v>5164.66</v>
       </c>
-      <c r="H19" s="95" t="n">
+      <c r="H19" s="96" t="n">
         <v>7041.14</v>
       </c>
-      <c r="I19" s="95"/>
-      <c r="J19" s="95"/>
-      <c r="K19" s="95"/>
-      <c r="L19" s="95"/>
-      <c r="M19" s="95"/>
+      <c r="I19" s="96"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="96"/>
+      <c r="L19" s="96"/>
+      <c r="M19" s="96"/>
       <c r="N19" s="75" t="n">
         <f aca="false">SUM(B19:M19)</f>
         <v>26909.12</v>
@@ -8830,636 +9191,1195 @@
       <c r="A20" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="B20" s="95" t="n">
+      <c r="B20" s="96" t="n">
         <v>18160.3</v>
       </c>
-      <c r="C20" s="95" t="n">
+      <c r="C20" s="96" t="n">
         <v>33566.6</v>
       </c>
-      <c r="D20" s="95" t="n">
+      <c r="D20" s="96" t="n">
         <v>37053.6</v>
       </c>
-      <c r="E20" s="95" t="n">
+      <c r="E20" s="96" t="n">
         <v>33728.59</v>
       </c>
-      <c r="F20" s="95" t="n">
+      <c r="F20" s="96" t="n">
         <v>46769.76</v>
       </c>
-      <c r="G20" s="95" t="n">
+      <c r="G20" s="96" t="n">
         <v>64034.11</v>
       </c>
-      <c r="H20" s="95" t="n">
+      <c r="H20" s="96" t="n">
         <v>91281.34</v>
       </c>
-      <c r="I20" s="95"/>
-      <c r="J20" s="95"/>
-      <c r="K20" s="95"/>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="96"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
       <c r="N20" s="75" t="n">
         <f aca="false">SUM(B20:M20)</f>
         <v>324594.3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="54" t="s">
         <v>293</v>
       </c>
-      <c r="B21" s="75" t="n">
-        <f aca="false">SUM(B15:B20)</f>
-        <v>26345.02</v>
-      </c>
-      <c r="C21" s="75" t="n">
-        <f aca="false">SUM(C15:C20)</f>
-        <v>37239.97</v>
-      </c>
-      <c r="D21" s="75" t="n">
-        <f aca="false">SUM(D15:D20)</f>
-        <v>40750.87</v>
-      </c>
-      <c r="E21" s="75" t="n">
-        <f aca="false">SUM(E15:E20)</f>
-        <v>38066.76</v>
-      </c>
-      <c r="F21" s="75" t="n">
-        <f aca="false">SUM(F15:F20)</f>
-        <v>51898.95</v>
-      </c>
-      <c r="G21" s="75" t="n">
-        <f aca="false">SUM(G15:G20)</f>
-        <v>70393.77</v>
-      </c>
-      <c r="H21" s="75" t="n">
-        <f aca="false">SUM(H15:H20)</f>
-        <v>99082.48</v>
-      </c>
-      <c r="I21" s="75" t="n">
-        <f aca="false">SUM(I15:I20)</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="75" t="n">
-        <f aca="false">SUM(J15:J20)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="75" t="n">
-        <f aca="false">SUM(K15:K20)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="75" t="n">
-        <f aca="false">SUM(L15:L20)</f>
-        <v>0</v>
-      </c>
-      <c r="M21" s="75" t="n">
-        <f aca="false">SUM(M15:M20)</f>
-        <v>0</v>
-      </c>
+      <c r="B21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="96"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
+      <c r="M21" s="96"/>
       <c r="N21" s="75" t="n">
-        <f aca="false">SUM(N15:N20)</f>
-        <v>363777.82</v>
+        <f aca="false">SUM(B21:M21)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="97" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" s="75" t="n">
+        <f aca="false">SUM(B15:B21)</f>
+        <v>26345.02</v>
+      </c>
+      <c r="C22" s="75" t="n">
+        <f aca="false">SUM(C15:C21)</f>
+        <v>37239.97</v>
+      </c>
+      <c r="D22" s="75" t="n">
+        <f aca="false">SUM(D15:D21)</f>
+        <v>40750.87</v>
+      </c>
+      <c r="E22" s="75" t="n">
+        <f aca="false">SUM(E15:E21)</f>
+        <v>38066.76</v>
+      </c>
+      <c r="F22" s="75" t="n">
+        <f aca="false">SUM(F15:F21)</f>
+        <v>51898.95</v>
+      </c>
+      <c r="G22" s="75" t="n">
+        <f aca="false">SUM(G15:G21)</f>
+        <v>70393.77</v>
+      </c>
+      <c r="H22" s="75" t="n">
+        <f aca="false">SUM(H15:H21)</f>
+        <v>99082.48</v>
+      </c>
+      <c r="I22" s="75" t="n">
+        <f aca="false">SUM(I15:I21)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="75" t="n">
+        <f aca="false">SUM(J15:J21)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="75" t="n">
+        <f aca="false">SUM(K15:K21)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="75" t="n">
+        <f aca="false">SUM(L15:L21)</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="75" t="n">
+        <f aca="false">SUM(M15:M21)</f>
+        <v>0</v>
+      </c>
+      <c r="N22" s="75" t="n">
+        <f aca="false">SUM(N15:N21)</f>
+        <v>363777.82</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="98" t="s">
         <v>251</v>
       </c>
-      <c r="B22" s="78" t="n">
-        <f aca="false">B13-B21</f>
+      <c r="B23" s="78" t="n">
+        <f aca="false">B13-B22</f>
         <v>38481.98</v>
       </c>
-      <c r="C22" s="78" t="n">
-        <f aca="false">C13-C21</f>
+      <c r="C23" s="78" t="n">
+        <f aca="false">C13-C22</f>
         <v>18578.78</v>
       </c>
-      <c r="D22" s="78" t="n">
-        <f aca="false">D13-D21</f>
+      <c r="D23" s="78" t="n">
+        <f aca="false">D13-D22</f>
         <v>62647.88</v>
       </c>
-      <c r="E22" s="78" t="n">
-        <f aca="false">E13-E21</f>
+      <c r="E23" s="78" t="n">
+        <f aca="false">E13-E22</f>
         <v>51397.49</v>
       </c>
-      <c r="F22" s="78" t="n">
-        <f aca="false">F13-F21</f>
+      <c r="F23" s="78" t="n">
+        <f aca="false">F13-F22</f>
         <v>48281.5</v>
       </c>
-      <c r="G22" s="78" t="n">
-        <f aca="false">G13-G21</f>
+      <c r="G23" s="78" t="n">
+        <f aca="false">G13-G22</f>
         <v>31730.23</v>
       </c>
-      <c r="H22" s="78" t="n">
-        <f aca="false">H13-H21</f>
+      <c r="H23" s="78" t="n">
+        <f aca="false">H13-H22</f>
         <v>77537.38</v>
       </c>
-      <c r="I22" s="78" t="n">
-        <f aca="false">I13-I21</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="78" t="n">
-        <f aca="false">J13-J21</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="78" t="n">
-        <f aca="false">K13-K21</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="78" t="n">
-        <f aca="false">L13-L21</f>
-        <v>0</v>
-      </c>
-      <c r="M22" s="78" t="n">
-        <f aca="false">M13-M21</f>
-        <v>0</v>
-      </c>
-      <c r="N22" s="78" t="n">
-        <f aca="false">N13-N21</f>
+      <c r="I23" s="78" t="n">
+        <f aca="false">I13-I22</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="78" t="n">
+        <f aca="false">J13-J22</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="78" t="n">
+        <f aca="false">K13-K22</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="78" t="n">
+        <f aca="false">L13-L22</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="78" t="n">
+        <f aca="false">M13-M22</f>
+        <v>0</v>
+      </c>
+      <c r="N23" s="78" t="n">
+        <f aca="false">N13-N22</f>
         <v>328655.24</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="54" t="s">
-        <v>294</v>
-      </c>
-      <c r="B23" s="95" t="n">
-        <v>6896.19</v>
-      </c>
-      <c r="C23" s="95" t="n">
-        <v>4395.76</v>
-      </c>
-      <c r="D23" s="95" t="n">
-        <v>6522.83</v>
-      </c>
-      <c r="E23" s="95" t="n">
-        <v>7155.22</v>
-      </c>
-      <c r="F23" s="95" t="n">
-        <v>11940.53</v>
-      </c>
-      <c r="G23" s="95" t="n">
-        <v>10475.28</v>
-      </c>
-      <c r="H23" s="95" t="n">
-        <v>11257.87</v>
-      </c>
-      <c r="I23" s="95"/>
-      <c r="J23" s="95"/>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="75" t="n">
-        <f aca="false">SUM(B23:M23)</f>
-        <v>58643.68</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="97" t="s">
+      <c r="A24" s="94" t="s">
         <v>295</v>
       </c>
-      <c r="B24" s="77" t="n">
-        <f aca="false">B22-B23</f>
-        <v>31585.79</v>
-      </c>
-      <c r="C24" s="77" t="n">
-        <f aca="false">C22-C23</f>
-        <v>14183.02</v>
-      </c>
-      <c r="D24" s="77" t="n">
-        <f aca="false">D22-D23</f>
-        <v>56125.05</v>
-      </c>
-      <c r="E24" s="77" t="n">
-        <f aca="false">E22-E23</f>
-        <v>44242.27</v>
-      </c>
-      <c r="F24" s="77" t="n">
-        <f aca="false">F22-F23</f>
-        <v>36340.97</v>
-      </c>
-      <c r="G24" s="77" t="n">
-        <f aca="false">G22-G23</f>
-        <v>21254.95</v>
-      </c>
-      <c r="H24" s="77" t="n">
-        <f aca="false">H22-H23</f>
-        <v>66279.51</v>
-      </c>
-      <c r="I24" s="77" t="n">
-        <f aca="false">I22-I23</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="77" t="n">
-        <f aca="false">J22-J23</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="77" t="n">
-        <f aca="false">K22-K23</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="77" t="n">
-        <f aca="false">L22-L23</f>
-        <v>0</v>
-      </c>
-      <c r="M24" s="77" t="n">
-        <f aca="false">M22-M23</f>
-        <v>0</v>
-      </c>
-      <c r="N24" s="77" t="n">
-        <f aca="false">N22-N23</f>
-        <v>270011.56</v>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="95"/>
+      <c r="N24" s="95"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="96" t="n">
+        <v>338</v>
+      </c>
+      <c r="H25" s="96" t="n">
+        <v>590.36</v>
+      </c>
+      <c r="I25" s="96"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="96"/>
+      <c r="L25" s="96"/>
+      <c r="M25" s="96"/>
+      <c r="N25" s="75" t="n">
+        <f aca="false">SUM(B25:M25)</f>
+        <v>928.36</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="53" t="s">
-        <v>296</v>
-      </c>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
+      <c r="A26" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="96" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="C26" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="96" t="n">
+        <v>48.99</v>
+      </c>
+      <c r="F26" s="96" t="n">
+        <v>71.42</v>
+      </c>
+      <c r="G26" s="96" t="n">
+        <v>73.52</v>
+      </c>
+      <c r="H26" s="96" t="n">
+        <v>68.63</v>
+      </c>
+      <c r="I26" s="96"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="96"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="96"/>
+      <c r="N26" s="75" t="n">
+        <f aca="false">SUM(B26:M26)</f>
+        <v>281.16</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="98"/>
-      <c r="B27" s="52" t="s">
-        <v>297</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>298</v>
-      </c>
-      <c r="D27" s="52" t="s">
-        <v>299</v>
-      </c>
-      <c r="E27" s="52" t="s">
-        <v>300</v>
+      <c r="A27" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="B27" s="96" t="n">
+        <v>100</v>
+      </c>
+      <c r="C27" s="96" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" s="96" t="n">
+        <v>100</v>
+      </c>
+      <c r="E27" s="96" t="n">
+        <v>100</v>
+      </c>
+      <c r="F27" s="96" t="n">
+        <v>185</v>
+      </c>
+      <c r="G27" s="96" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="H27" s="96" t="n">
+        <v>252.57</v>
+      </c>
+      <c r="I27" s="96"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="96"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="96"/>
+      <c r="N27" s="75" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>960.56</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="B28" s="96" t="n">
+        <v>148.98</v>
+      </c>
+      <c r="C28" s="96" t="n">
+        <v>163.14</v>
+      </c>
+      <c r="D28" s="96" t="n">
+        <v>203.88</v>
+      </c>
+      <c r="E28" s="96" t="n">
+        <v>171.34</v>
+      </c>
+      <c r="F28" s="96" t="n">
+        <v>168.44</v>
+      </c>
+      <c r="G28" s="96" t="n">
+        <v>174.18</v>
+      </c>
+      <c r="H28" s="96" t="n">
+        <v>194.18</v>
+      </c>
+      <c r="I28" s="96"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="96"/>
+      <c r="L28" s="96"/>
+      <c r="M28" s="96"/>
+      <c r="N28" s="75" t="n">
+        <f aca="false">SUM(B28:M28)</f>
+        <v>1224.14</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="96"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="96"/>
+      <c r="L29" s="96"/>
+      <c r="M29" s="96"/>
+      <c r="N29" s="75" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="96" t="n">
+        <v>399.75</v>
+      </c>
+      <c r="C30" s="96" t="n">
+        <v>293.25</v>
+      </c>
+      <c r="D30" s="96" t="n">
+        <v>1471.25</v>
+      </c>
+      <c r="E30" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="96" t="n">
+        <v>3419.63</v>
+      </c>
+      <c r="G30" s="96" t="n">
+        <v>5300</v>
+      </c>
+      <c r="H30" s="96" t="n">
+        <v>5200</v>
+      </c>
+      <c r="I30" s="96"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="96"/>
+      <c r="L30" s="96"/>
+      <c r="M30" s="96"/>
+      <c r="N30" s="75" t="n">
+        <f aca="false">SUM(B30:M30)</f>
+        <v>16083.88</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="B31" s="96" t="n">
+        <v>539.3</v>
+      </c>
+      <c r="C31" s="96" t="n">
+        <v>439.55</v>
+      </c>
+      <c r="D31" s="96" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="E31" s="96" t="n">
+        <v>486.47</v>
+      </c>
+      <c r="F31" s="96" t="n">
+        <v>579.59</v>
+      </c>
+      <c r="G31" s="96" t="n">
+        <v>160.62</v>
+      </c>
+      <c r="H31" s="96" t="n">
+        <v>202.85</v>
+      </c>
+      <c r="I31" s="96"/>
+      <c r="J31" s="96"/>
+      <c r="K31" s="96"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="75" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>2728.15</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="96" t="n">
+        <v>2705.65</v>
+      </c>
+      <c r="C32" s="96" t="n">
+        <v>1598.23</v>
+      </c>
+      <c r="D32" s="96" t="n">
+        <v>2648.42</v>
+      </c>
+      <c r="E32" s="96" t="n">
+        <v>3059.94</v>
+      </c>
+      <c r="F32" s="96" t="n">
+        <v>1942.95</v>
+      </c>
+      <c r="G32" s="96" t="n">
+        <v>2497.17</v>
+      </c>
+      <c r="H32" s="96" t="n">
+        <v>3145.14</v>
+      </c>
+      <c r="I32" s="96"/>
+      <c r="J32" s="96"/>
+      <c r="K32" s="96"/>
+      <c r="L32" s="96"/>
+      <c r="M32" s="96"/>
+      <c r="N32" s="75" t="n">
+        <f aca="false">SUM(B32:M32)</f>
+        <v>17597.5</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" s="96" t="n">
+        <v>1630</v>
+      </c>
+      <c r="C33" s="96" t="n">
+        <v>340</v>
+      </c>
+      <c r="D33" s="96" t="n">
+        <v>280</v>
+      </c>
+      <c r="E33" s="96" t="n">
+        <v>1790</v>
+      </c>
+      <c r="F33" s="96" t="n">
+        <v>4096</v>
+      </c>
+      <c r="G33" s="96" t="n">
+        <v>280</v>
+      </c>
+      <c r="H33" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="96"/>
+      <c r="J33" s="96"/>
+      <c r="K33" s="96"/>
+      <c r="L33" s="96"/>
+      <c r="M33" s="96"/>
+      <c r="N33" s="75" t="n">
+        <f aca="false">SUM(B33:M33)</f>
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="B34" s="96" t="n">
+        <v>162.91</v>
+      </c>
+      <c r="C34" s="96" t="n">
+        <v>244.59</v>
+      </c>
+      <c r="D34" s="96" t="n">
+        <v>295.51</v>
+      </c>
+      <c r="E34" s="96" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="F34" s="96" t="n">
+        <v>222.15</v>
+      </c>
+      <c r="G34" s="96" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="H34" s="96" t="n">
+        <v>404.14</v>
+      </c>
+      <c r="I34" s="96"/>
+      <c r="J34" s="96"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
+      <c r="M34" s="96"/>
+      <c r="N34" s="75" t="n">
+        <f aca="false">SUM(B34:M34)</f>
+        <v>1749.22</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="B35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="96" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="96" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="G35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="96"/>
+      <c r="J35" s="96"/>
+      <c r="K35" s="96"/>
+      <c r="L35" s="96"/>
+      <c r="M35" s="96"/>
+      <c r="N35" s="75" t="n">
+        <f aca="false">SUM(B35:M35)</f>
+        <v>67.35</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="B36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H36" s="96" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I36" s="96"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="96"/>
+      <c r="L36" s="96"/>
+      <c r="M36" s="96"/>
+      <c r="N36" s="75" t="n">
+        <f aca="false">SUM(B36:M36)</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="B37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="96"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="96"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="75" t="n">
+        <f aca="false">SUM(B37:M37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="B38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="96" t="n">
+        <v>207.36</v>
+      </c>
+      <c r="F38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="96"/>
+      <c r="J38" s="96"/>
+      <c r="K38" s="96"/>
+      <c r="L38" s="96"/>
+      <c r="M38" s="96"/>
+      <c r="N38" s="75" t="n">
+        <f aca="false">SUM(B38:M38)</f>
+        <v>207.36</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="B39" s="75" t="n">
+        <f aca="false">SUM(B25:B38)</f>
+        <v>6896.19</v>
+      </c>
+      <c r="C39" s="75" t="n">
+        <f aca="false">SUM(C25:C38)</f>
+        <v>4395.76</v>
+      </c>
+      <c r="D39" s="75" t="n">
+        <f aca="false">SUM(D25:D38)</f>
+        <v>6522.83</v>
+      </c>
+      <c r="E39" s="75" t="n">
+        <f aca="false">SUM(E25:E38)</f>
+        <v>7155.22</v>
+      </c>
+      <c r="F39" s="75" t="n">
+        <f aca="false">SUM(F25:F38)</f>
+        <v>11940.53</v>
+      </c>
+      <c r="G39" s="75" t="n">
+        <f aca="false">SUM(G25:G38)</f>
+        <v>10475.28</v>
+      </c>
+      <c r="H39" s="75" t="n">
+        <f aca="false">SUM(H25:H38)</f>
+        <v>11257.87</v>
+      </c>
+      <c r="I39" s="75" t="n">
+        <f aca="false">SUM(I25:I38)</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="75" t="n">
+        <f aca="false">SUM(J25:J38)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="75" t="n">
+        <f aca="false">SUM(K25:K38)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="75" t="n">
+        <f aca="false">SUM(L25:L38)</f>
+        <v>0</v>
+      </c>
+      <c r="M39" s="75" t="n">
+        <f aca="false">SUM(M25:M38)</f>
+        <v>0</v>
+      </c>
+      <c r="N39" s="75" t="n">
+        <f aca="false">SUM(N25:N38)</f>
+        <v>58643.68</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="B40" s="77" t="n">
+        <f aca="false">B23-B39</f>
+        <v>31585.79</v>
+      </c>
+      <c r="C40" s="77" t="n">
+        <f aca="false">C23-C39</f>
+        <v>14183.02</v>
+      </c>
+      <c r="D40" s="77" t="n">
+        <f aca="false">D23-D39</f>
+        <v>56125.05</v>
+      </c>
+      <c r="E40" s="77" t="n">
+        <f aca="false">E23-E39</f>
+        <v>44242.27</v>
+      </c>
+      <c r="F40" s="77" t="n">
+        <f aca="false">F23-F39</f>
+        <v>36340.97</v>
+      </c>
+      <c r="G40" s="77" t="n">
+        <f aca="false">G23-G39</f>
+        <v>21254.95</v>
+      </c>
+      <c r="H40" s="77" t="n">
+        <f aca="false">H23-H39</f>
+        <v>66279.51</v>
+      </c>
+      <c r="I40" s="77" t="n">
+        <f aca="false">I23-I39</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="77" t="n">
+        <f aca="false">J23-J39</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="77" t="n">
+        <f aca="false">K23-K39</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="77" t="n">
+        <f aca="false">L23-L39</f>
+        <v>0</v>
+      </c>
+      <c r="M40" s="77" t="n">
+        <f aca="false">M23-M39</f>
+        <v>0</v>
+      </c>
+      <c r="N40" s="77" t="n">
+        <f aca="false">N23-N39</f>
+        <v>270011.56</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="53" t="s">
+        <v>300</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="99"/>
+      <c r="B43" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>303</v>
+      </c>
+      <c r="E43" s="52" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="54" t="s">
         <v>288</v>
       </c>
-      <c r="B28" s="99" t="n">
+      <c r="B44" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$10:INDEX('Budget P&amp;L'!$B$10:$M$10,1,$B$6))</f>
         <v>763218.198412699</v>
       </c>
-      <c r="C28" s="74" t="n">
+      <c r="C44" s="74" t="n">
         <f aca="false">SUM($B$13:INDEX($B$13:$M$13,1,$B$6))</f>
         <v>692433.06</v>
       </c>
-      <c r="D28" s="74" t="n">
-        <f aca="false">(C28-B28)</f>
+      <c r="D44" s="74" t="n">
+        <f aca="false">(C44-B44)</f>
         <v>-70785.1384126984</v>
       </c>
-      <c r="E28" s="100" t="n">
-        <f aca="false">IF(B28=0,0,D28/ABS(B28))</f>
+      <c r="E44" s="101" t="n">
+        <f aca="false">IF(B44=0,0,D44/ABS(B44))</f>
         <v>-0.0927456113597837</v>
       </c>
-      <c r="F28" s="63" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="54" t="s">
-        <v>293</v>
-      </c>
-      <c r="B29" s="99" t="n">
+      <c r="F44" s="63" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B45" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$21:INDEX('Budget P&amp;L'!$B$21:$M$21,1,$B$6))</f>
         <v>350722.68625</v>
       </c>
-      <c r="C29" s="74" t="n">
-        <f aca="false">SUM($B$21:INDEX($B$21:$M$21,1,$B$6))</f>
+      <c r="C45" s="74" t="n">
+        <f aca="false">SUM($B$22:INDEX($B$22:$M$22,1,$B$6))</f>
         <v>363777.82</v>
       </c>
-      <c r="D29" s="74" t="n">
-        <f aca="false">(B29-C29)</f>
+      <c r="D45" s="74" t="n">
+        <f aca="false">(B45-C45)</f>
         <v>-13055.13375</v>
       </c>
-      <c r="E29" s="100" t="n">
-        <f aca="false">IF(B29=0,0,D29/ABS(B29))</f>
+      <c r="E45" s="101" t="n">
+        <f aca="false">IF(B45=0,0,D45/ABS(B45))</f>
         <v>-0.0372235223492049</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="54" t="s">
         <v>251</v>
       </c>
-      <c r="B30" s="99" t="n">
+      <c r="B46" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$22:INDEX('Budget P&amp;L'!$B$22:$M$22,1,$B$6))</f>
         <v>412495.512162699</v>
       </c>
-      <c r="C30" s="74" t="n">
-        <f aca="false">SUM($B$22:INDEX($B$22:$M$22,1,$B$6))</f>
+      <c r="C46" s="74" t="n">
+        <f aca="false">SUM($B$23:INDEX($B$23:$M$23,1,$B$6))</f>
         <v>328655.24</v>
       </c>
-      <c r="D30" s="74" t="n">
-        <f aca="false">(C30-B30)</f>
+      <c r="D46" s="74" t="n">
+        <f aca="false">(C46-B46)</f>
         <v>-83840.2721626985</v>
       </c>
-      <c r="E30" s="100" t="n">
-        <f aca="false">IF(B30=0,0,D30/ABS(B30))</f>
+      <c r="E46" s="101" t="n">
+        <f aca="false">IF(B46=0,0,D46/ABS(B46))</f>
         <v>-0.203251355931431</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="54" t="s">
-        <v>302</v>
-      </c>
-      <c r="B31" s="99" t="n">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="54" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$40:INDEX('Budget P&amp;L'!$B$40:$M$40,1,$B$6))</f>
         <v>161825.687916667</v>
       </c>
-      <c r="C31" s="74" t="n">
-        <f aca="false">SUM($B$23:INDEX($B$23:$M$23,1,$B$6))</f>
+      <c r="C47" s="74" t="n">
+        <f aca="false">SUM($B$39:INDEX($B$39:$M$39,1,$B$6))</f>
         <v>58643.68</v>
       </c>
-      <c r="D31" s="74" t="n">
-        <f aca="false">(B31-C31)</f>
+      <c r="D47" s="74" t="n">
+        <f aca="false">(B47-C47)</f>
         <v>103182.007916667</v>
       </c>
-      <c r="E31" s="100" t="n">
-        <f aca="false">IF(B31=0,0,D31/ABS(B31))</f>
+      <c r="E47" s="101" t="n">
+        <f aca="false">IF(B47=0,0,D47/ABS(B47))</f>
         <v>0.637612045683384</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="71" t="s">
-        <v>303</v>
-      </c>
-      <c r="B32" s="101" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="71" t="s">
+        <v>306</v>
+      </c>
+      <c r="B48" s="102" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$42:INDEX('Budget P&amp;L'!$B$42:$M$42,1,$B$6))</f>
         <v>250669.824246032</v>
       </c>
-      <c r="C32" s="102" t="n">
-        <f aca="false">SUM($B$24:INDEX($B$24:$M$24,1,$B$6))</f>
+      <c r="C48" s="103" t="n">
+        <f aca="false">SUM($B$40:INDEX($B$40:$M$40,1,$B$6))</f>
         <v>270011.56</v>
       </c>
-      <c r="D32" s="102" t="n">
-        <f aca="false">(C32-B32)</f>
+      <c r="D48" s="103" t="n">
+        <f aca="false">(C48-B48)</f>
         <v>19341.7357539682</v>
       </c>
-      <c r="E32" s="103" t="n">
-        <f aca="false">IF(B32=0,0,D32/ABS(B32))</f>
+      <c r="E48" s="104" t="n">
+        <f aca="false">IF(B48=0,0,D48/ABS(B48))</f>
         <v>0.077160207903542</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="53" t="s">
-        <v>304</v>
-      </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="104" t="s">
-        <v>305</v>
-      </c>
-      <c r="B36" s="105" t="s">
-        <v>306</v>
-      </c>
-      <c r="C36" s="104" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="58" t="s">
         <v>307</v>
       </c>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="104"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="104"/>
-    </row>
-    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54" t="s">
+      <c r="B50" s="105" t="n">
+        <f aca="false">IF(B44=0,0,C44/(B44/Assumptions!$B$15))</f>
+        <v>0.907254388640216</v>
+      </c>
+      <c r="C50" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="B37" s="99" t="n">
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="53" t="s">
+        <v>309</v>
+      </c>
+      <c r="B52" s="51"/>
+      <c r="C52" s="51"/>
+      <c r="D52" s="51"/>
+      <c r="E52" s="51"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="106" t="s">
+        <v>310</v>
+      </c>
+      <c r="B53" s="107" t="s">
+        <v>311</v>
+      </c>
+      <c r="C53" s="106" t="s">
+        <v>312</v>
+      </c>
+      <c r="D53" s="106"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="106"/>
+      <c r="G53" s="106"/>
+      <c r="H53" s="106"/>
+      <c r="I53" s="106"/>
+      <c r="J53" s="106"/>
+      <c r="K53" s="106"/>
+      <c r="L53" s="106"/>
+      <c r="M53" s="106"/>
+    </row>
+    <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="54" t="s">
+        <v>313</v>
+      </c>
+      <c r="B54" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$24:INDEX('Budget P&amp;L'!$B$24:$M$24,1,$B$6))</f>
         <v>53812.5</v>
       </c>
-      <c r="C37" s="106" t="s">
-        <v>309</v>
-      </c>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="106"/>
-      <c r="G37" s="106"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-    </row>
-    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54" t="s">
-        <v>310</v>
-      </c>
-      <c r="B38" s="99" t="n">
+      <c r="C54" s="108" t="s">
+        <v>314</v>
+      </c>
+      <c r="D54" s="108"/>
+      <c r="E54" s="108"/>
+      <c r="F54" s="108"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="108"/>
+      <c r="I54" s="108"/>
+      <c r="J54" s="108"/>
+      <c r="K54" s="108"/>
+      <c r="L54" s="108"/>
+      <c r="M54" s="108"/>
+    </row>
+    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="54" t="s">
+        <v>315</v>
+      </c>
+      <c r="B55" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$25:INDEX('Budget P&amp;L'!$B$25:$M$25,1,$B$6))</f>
         <v>39666.6666666667</v>
       </c>
-      <c r="C38" s="106" t="s">
-        <v>311</v>
-      </c>
-      <c r="D38" s="106"/>
-      <c r="E38" s="106"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="106"/>
-      <c r="H38" s="106"/>
-      <c r="I38" s="106"/>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="106"/>
-    </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="54" t="s">
-        <v>312</v>
-      </c>
-      <c r="B39" s="99" t="n">
+      <c r="C55" s="108" t="s">
+        <v>316</v>
+      </c>
+      <c r="D55" s="108"/>
+      <c r="E55" s="108"/>
+      <c r="F55" s="108"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="108"/>
+      <c r="I55" s="108"/>
+      <c r="J55" s="108"/>
+      <c r="K55" s="108"/>
+      <c r="L55" s="108"/>
+      <c r="M55" s="108"/>
+    </row>
+    <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="54" t="s">
+        <v>317</v>
+      </c>
+      <c r="B56" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$26:INDEX('Budget P&amp;L'!$B$26:$M$26,1,$B$6))</f>
         <v>7271.80125</v>
       </c>
-      <c r="C39" s="106" t="s">
-        <v>313</v>
-      </c>
-      <c r="D39" s="106"/>
-      <c r="E39" s="106"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="106"/>
-      <c r="H39" s="106"/>
-      <c r="I39" s="106"/>
-      <c r="J39" s="106"/>
-      <c r="K39" s="106"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="106"/>
-    </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="54" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" s="99" t="n">
+      <c r="C56" s="108" t="s">
+        <v>318</v>
+      </c>
+      <c r="D56" s="108"/>
+      <c r="E56" s="108"/>
+      <c r="F56" s="108"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="108"/>
+      <c r="I56" s="108"/>
+      <c r="J56" s="108"/>
+      <c r="K56" s="108"/>
+      <c r="L56" s="108"/>
+      <c r="M56" s="108"/>
+    </row>
+    <row r="57" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="B57" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$19:INDEX('Budget P&amp;L'!$B$19:$M$19,1,$B$6))+SUM('Budget P&amp;L'!$B$27:INDEX('Budget P&amp;L'!$B$27:$M$27,1,$B$6))</f>
         <v>28000</v>
       </c>
-      <c r="C40" s="106" t="s">
-        <v>315</v>
-      </c>
-      <c r="D40" s="106"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="106"/>
-      <c r="G40" s="106"/>
-      <c r="H40" s="106"/>
-      <c r="I40" s="106"/>
-      <c r="J40" s="106"/>
-      <c r="K40" s="106"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="106"/>
-    </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="54" t="s">
+      <c r="C57" s="108" t="s">
+        <v>320</v>
+      </c>
+      <c r="D57" s="108"/>
+      <c r="E57" s="108"/>
+      <c r="F57" s="108"/>
+      <c r="G57" s="108"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="108"/>
+      <c r="J57" s="108"/>
+      <c r="K57" s="108"/>
+      <c r="L57" s="108"/>
+      <c r="M57" s="108"/>
+    </row>
+    <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="54" t="s">
         <v>264</v>
       </c>
-      <c r="B41" s="99" t="n">
+      <c r="B58" s="100" t="n">
         <f aca="false">SUM('Budget P&amp;L'!$B$32:INDEX('Budget P&amp;L'!$B$32:$M$32,1,$B$6))</f>
         <v>8050</v>
       </c>
-      <c r="C41" s="106" t="s">
-        <v>316</v>
-      </c>
-      <c r="D41" s="106"/>
-      <c r="E41" s="106"/>
-      <c r="F41" s="106"/>
-      <c r="G41" s="106"/>
-      <c r="H41" s="106"/>
-      <c r="I41" s="106"/>
-      <c r="J41" s="106"/>
-      <c r="K41" s="106"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="106"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71" t="s">
-        <v>317</v>
-      </c>
-      <c r="B42" s="78" t="n">
-        <f aca="false">SUM(B37:B41)</f>
+      <c r="C58" s="108" t="s">
+        <v>321</v>
+      </c>
+      <c r="D58" s="108"/>
+      <c r="E58" s="108"/>
+      <c r="F58" s="108"/>
+      <c r="G58" s="108"/>
+      <c r="H58" s="108"/>
+      <c r="I58" s="108"/>
+      <c r="J58" s="108"/>
+      <c r="K58" s="108"/>
+      <c r="L58" s="108"/>
+      <c r="M58" s="108"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="B59" s="78" t="n">
+        <f aca="false">SUM(B54:B58)</f>
         <v>136800.967916667</v>
       </c>
-      <c r="C42" s="107" t="s">
-        <v>318</v>
-      </c>
-      <c r="D42" s="107"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="107"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="107"/>
-      <c r="I42" s="107"/>
-      <c r="J42" s="107"/>
-      <c r="K42" s="107"/>
-      <c r="L42" s="107"/>
-      <c r="M42" s="107"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="108" t="s">
-        <v>319</v>
-      </c>
-      <c r="B44" s="108"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="108"/>
-      <c r="E44" s="108"/>
-      <c r="F44" s="108"/>
-      <c r="G44" s="108"/>
-      <c r="H44" s="108"/>
-      <c r="I44" s="108"/>
-      <c r="J44" s="108"/>
-      <c r="K44" s="108"/>
-      <c r="L44" s="108"/>
-      <c r="M44" s="108"/>
-    </row>
-    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="106" t="s">
-        <v>320</v>
-      </c>
-      <c r="B45" s="106"/>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="106"/>
-      <c r="H45" s="106"/>
-      <c r="I45" s="106"/>
-      <c r="J45" s="106"/>
-      <c r="K45" s="106"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="106"/>
-    </row>
-    <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="106" t="s">
-        <v>321</v>
-      </c>
-      <c r="B46" s="106"/>
-      <c r="C46" s="106"/>
-      <c r="D46" s="106"/>
-      <c r="E46" s="106"/>
-      <c r="F46" s="106"/>
-      <c r="G46" s="106"/>
-      <c r="H46" s="106"/>
-      <c r="I46" s="106"/>
-      <c r="J46" s="106"/>
-      <c r="K46" s="106"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="106"/>
-    </row>
-    <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="106" t="s">
-        <v>322</v>
-      </c>
-      <c r="B47" s="106"/>
-      <c r="C47" s="106"/>
-      <c r="D47" s="106"/>
-      <c r="E47" s="106"/>
-      <c r="F47" s="106"/>
-      <c r="G47" s="106"/>
-      <c r="H47" s="106"/>
-      <c r="I47" s="106"/>
-      <c r="J47" s="106"/>
-      <c r="K47" s="106"/>
-      <c r="L47" s="106"/>
-      <c r="M47" s="106"/>
-    </row>
-    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="106" t="s">
+      <c r="C59" s="109" t="s">
         <v>323</v>
       </c>
-      <c r="B48" s="106"/>
-      <c r="C48" s="106"/>
-      <c r="D48" s="106"/>
-      <c r="E48" s="106"/>
-      <c r="F48" s="106"/>
-      <c r="G48" s="106"/>
-      <c r="H48" s="106"/>
-      <c r="I48" s="106"/>
-      <c r="J48" s="106"/>
-      <c r="K48" s="106"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="106"/>
+      <c r="D59" s="109"/>
+      <c r="E59" s="109"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="109"/>
+      <c r="H59" s="109"/>
+      <c r="I59" s="109"/>
+      <c r="J59" s="109"/>
+      <c r="K59" s="109"/>
+      <c r="L59" s="109"/>
+      <c r="M59" s="109"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="110" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="110"/>
+      <c r="C61" s="110"/>
+      <c r="D61" s="110"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="110"/>
+      <c r="G61" s="110"/>
+      <c r="H61" s="110"/>
+      <c r="I61" s="110"/>
+      <c r="J61" s="110"/>
+      <c r="K61" s="110"/>
+      <c r="L61" s="110"/>
+      <c r="M61" s="110"/>
+    </row>
+    <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="108" t="s">
+        <v>325</v>
+      </c>
+      <c r="B62" s="108"/>
+      <c r="C62" s="108"/>
+      <c r="D62" s="108"/>
+      <c r="E62" s="108"/>
+      <c r="F62" s="108"/>
+      <c r="G62" s="108"/>
+      <c r="H62" s="108"/>
+      <c r="I62" s="108"/>
+      <c r="J62" s="108"/>
+      <c r="K62" s="108"/>
+      <c r="L62" s="108"/>
+      <c r="M62" s="108"/>
+    </row>
+    <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="108" t="s">
+        <v>326</v>
+      </c>
+      <c r="B63" s="108"/>
+      <c r="C63" s="108"/>
+      <c r="D63" s="108"/>
+      <c r="E63" s="108"/>
+      <c r="F63" s="108"/>
+      <c r="G63" s="108"/>
+      <c r="H63" s="108"/>
+      <c r="I63" s="108"/>
+      <c r="J63" s="108"/>
+      <c r="K63" s="108"/>
+      <c r="L63" s="108"/>
+      <c r="M63" s="108"/>
+    </row>
+    <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="108" t="s">
+        <v>327</v>
+      </c>
+      <c r="B64" s="108"/>
+      <c r="C64" s="108"/>
+      <c r="D64" s="108"/>
+      <c r="E64" s="108"/>
+      <c r="F64" s="108"/>
+      <c r="G64" s="108"/>
+      <c r="H64" s="108"/>
+      <c r="I64" s="108"/>
+      <c r="J64" s="108"/>
+      <c r="K64" s="108"/>
+      <c r="L64" s="108"/>
+      <c r="M64" s="108"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="C36:M36"/>
-    <mergeCell ref="C37:M37"/>
-    <mergeCell ref="C38:M38"/>
-    <mergeCell ref="C39:M39"/>
-    <mergeCell ref="C40:M40"/>
-    <mergeCell ref="C41:M41"/>
-    <mergeCell ref="C42:M42"/>
-    <mergeCell ref="A44:M44"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A48:M48"/>
+  <mergeCells count="11">
+    <mergeCell ref="C53:M53"/>
+    <mergeCell ref="C54:M54"/>
+    <mergeCell ref="C55:M55"/>
+    <mergeCell ref="C56:M56"/>
+    <mergeCell ref="C57:M57"/>
+    <mergeCell ref="C58:M58"/>
+    <mergeCell ref="C59:M59"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A62:M62"/>
+    <mergeCell ref="A63:M63"/>
+    <mergeCell ref="A64:M64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9475,9 +10395,2347 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:N61"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="49" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="50" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="B5" s="111" t="n">
+        <f aca="false">'Budget vs Actual'!$B$6</f>
+        <v>7</v>
+      </c>
+      <c r="C5" s="112" t="str">
+        <f aca="false">IF($B$5=0,"all budget",INDEX({"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec"},1,$B$5))</f>
+        <v>Jul</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="113" t="n">
+        <f aca="false">Assumptions!$B$15</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="114" t="n">
+        <f aca="false">'Budget vs Actual'!$B$50</f>
+        <v>0.907254388640216</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="51"/>
+      <c r="B8" s="52" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="F8" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>175</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>178</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="N8" s="52" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="115" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="116" t="str">
+        <f aca="false">IF(1&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="C9" s="116" t="str">
+        <f aca="false">IF(2&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="D9" s="116" t="str">
+        <f aca="false">IF(3&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="E9" s="116" t="str">
+        <f aca="false">IF(4&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="F9" s="116" t="str">
+        <f aca="false">IF(5&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="G9" s="116" t="str">
+        <f aca="false">IF(6&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="H9" s="116" t="str">
+        <f aca="false">IF(7&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>ACTUAL</v>
+      </c>
+      <c r="I9" s="116" t="str">
+        <f aca="false">IF(8&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>BUDGET</v>
+      </c>
+      <c r="J9" s="116" t="str">
+        <f aca="false">IF(9&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>BUDGET</v>
+      </c>
+      <c r="K9" s="116" t="str">
+        <f aca="false">IF(10&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>BUDGET</v>
+      </c>
+      <c r="L9" s="116" t="str">
+        <f aca="false">IF(11&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>BUDGET</v>
+      </c>
+      <c r="M9" s="116" t="str">
+        <f aca="false">IF(12&lt;=$B$5,"ACTUAL","BUDGET")</f>
+        <v>BUDGET</v>
+      </c>
+      <c r="N9" s="117" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="53" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="54" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B10,'Budget P&amp;L'!B8)</f>
+        <v>0</v>
+      </c>
+      <c r="C11" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C10,'Budget P&amp;L'!C8)</f>
+        <v>46.75</v>
+      </c>
+      <c r="D11" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D10,'Budget P&amp;L'!D8)</f>
+        <v>21</v>
+      </c>
+      <c r="E11" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E10,'Budget P&amp;L'!E8)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F10,'Budget P&amp;L'!F8)</f>
+        <v>2294</v>
+      </c>
+      <c r="G11" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G10,'Budget P&amp;L'!G8)</f>
+        <v>-418</v>
+      </c>
+      <c r="H11" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H10,'Budget P&amp;L'!H8)</f>
+        <v>-152.69</v>
+      </c>
+      <c r="I11" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I10,'Budget P&amp;L'!I8)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J10,'Budget P&amp;L'!J8)</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K10,'Budget P&amp;L'!K8)</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L10,'Budget P&amp;L'!L8)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M10,'Budget P&amp;L'!M8)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="75" t="n">
+        <f aca="false">SUM(B11:M11)</f>
+        <v>1791.06</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B11,'Budget P&amp;L'!B9)</f>
+        <v>64981.75</v>
+      </c>
+      <c r="C12" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C11,'Budget P&amp;L'!C9)</f>
+        <v>55772</v>
+      </c>
+      <c r="D12" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D11,'Budget P&amp;L'!D9)</f>
+        <v>103377.75</v>
+      </c>
+      <c r="E12" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E11,'Budget P&amp;L'!E9)</f>
+        <v>88464.25</v>
+      </c>
+      <c r="F12" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F11,'Budget P&amp;L'!F9)</f>
+        <v>97011.45</v>
+      </c>
+      <c r="G12" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G11,'Budget P&amp;L'!G9)</f>
+        <v>104042</v>
+      </c>
+      <c r="H12" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H11,'Budget P&amp;L'!H9)</f>
+        <v>177147.55</v>
+      </c>
+      <c r="I12" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I11,'Budget P&amp;L'!I9)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="J12" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J11,'Budget P&amp;L'!J9)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="K12" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K11,'Budget P&amp;L'!K9)</f>
+        <v>113232.76984127</v>
+      </c>
+      <c r="L12" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L11,'Budget P&amp;L'!L9)</f>
+        <v>101468.293650794</v>
+      </c>
+      <c r="M12" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M11,'Budget P&amp;L'!M9)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="N12" s="75" t="n">
+        <f aca="false">SUM(B12:M12)</f>
+        <v>1227549.40873016</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="54" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B12,0)</f>
+        <v>-154.75</v>
+      </c>
+      <c r="C13" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E12,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="F13" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F12,0)</f>
+        <v>875</v>
+      </c>
+      <c r="G13" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G12,0)</f>
+        <v>-1500</v>
+      </c>
+      <c r="H13" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H12,0)</f>
+        <v>-375</v>
+      </c>
+      <c r="I13" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="75" t="n">
+        <f aca="false">SUM(B13:M13)</f>
+        <v>-154.75</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="97" t="s">
+        <v>288</v>
+      </c>
+      <c r="B14" s="75" t="n">
+        <f aca="false">SUM(B11:B13)</f>
+        <v>64827</v>
+      </c>
+      <c r="C14" s="75" t="n">
+        <f aca="false">SUM(C11:C13)</f>
+        <v>55818.75</v>
+      </c>
+      <c r="D14" s="75" t="n">
+        <f aca="false">SUM(D11:D13)</f>
+        <v>103398.75</v>
+      </c>
+      <c r="E14" s="75" t="n">
+        <f aca="false">SUM(E11:E13)</f>
+        <v>89464.25</v>
+      </c>
+      <c r="F14" s="75" t="n">
+        <f aca="false">SUM(F11:F13)</f>
+        <v>100180.45</v>
+      </c>
+      <c r="G14" s="75" t="n">
+        <f aca="false">SUM(G11:G13)</f>
+        <v>102124</v>
+      </c>
+      <c r="H14" s="75" t="n">
+        <f aca="false">SUM(H11:H13)</f>
+        <v>176619.86</v>
+      </c>
+      <c r="I14" s="75" t="n">
+        <f aca="false">SUM(I11:I13)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="J14" s="75" t="n">
+        <f aca="false">SUM(J11:J13)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="K14" s="75" t="n">
+        <f aca="false">SUM(K11:K13)</f>
+        <v>113232.76984127</v>
+      </c>
+      <c r="L14" s="75" t="n">
+        <f aca="false">SUM(L11:L13)</f>
+        <v>101468.293650794</v>
+      </c>
+      <c r="M14" s="75" t="n">
+        <f aca="false">SUM(M11:M13)</f>
+        <v>107350.531746032</v>
+      </c>
+      <c r="N14" s="75" t="n">
+        <f aca="false">SUM(N11:N13)</f>
+        <v>1229185.71873016</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="53" t="s">
+        <v>338</v>
+      </c>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="51"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="B16" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B15,'Budget P&amp;L'!B12)</f>
+        <v>1498.5</v>
+      </c>
+      <c r="C16" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C15,'Budget P&amp;L'!C12)</f>
+        <v>430</v>
+      </c>
+      <c r="D16" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D15,'Budget P&amp;L'!D12)</f>
+        <v>355.5</v>
+      </c>
+      <c r="E16" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E15,'Budget P&amp;L'!E12)</f>
+        <v>1089.5</v>
+      </c>
+      <c r="F16" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F15,'Budget P&amp;L'!F12)</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G15,'Budget P&amp;L'!G12)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H15,'Budget P&amp;L'!H12)</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I15,'Budget P&amp;L'!I12)</f>
+        <v>4200</v>
+      </c>
+      <c r="J16" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J15,'Budget P&amp;L'!J12)</f>
+        <v>4200</v>
+      </c>
+      <c r="K16" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K15,'Budget P&amp;L'!K12)</f>
+        <v>4200</v>
+      </c>
+      <c r="L16" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L15,'Budget P&amp;L'!L12)</f>
+        <v>4200</v>
+      </c>
+      <c r="M16" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M15,'Budget P&amp;L'!M12)</f>
+        <v>4200</v>
+      </c>
+      <c r="N16" s="75" t="n">
+        <f aca="false">SUM(B16:M16)</f>
+        <v>24373.5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="54" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B16,'Budget P&amp;L'!B13)</f>
+        <v>94.5</v>
+      </c>
+      <c r="C17" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C16,'Budget P&amp;L'!C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D16,'Budget P&amp;L'!D13)</f>
+        <v>13.2</v>
+      </c>
+      <c r="E17" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E16,'Budget P&amp;L'!E13)</f>
+        <v>63.2</v>
+      </c>
+      <c r="F17" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F16,'Budget P&amp;L'!F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G16,'Budget P&amp;L'!G13)</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H16,'Budget P&amp;L'!H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I16,'Budget P&amp;L'!I13)</f>
+        <v>28.48</v>
+      </c>
+      <c r="J17" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J16,'Budget P&amp;L'!J13)</f>
+        <v>28.48</v>
+      </c>
+      <c r="K17" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K16,'Budget P&amp;L'!K13)</f>
+        <v>28.48</v>
+      </c>
+      <c r="L17" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L16,'Budget P&amp;L'!L13)</f>
+        <v>28.48</v>
+      </c>
+      <c r="M17" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M16,'Budget P&amp;L'!M13)</f>
+        <v>28.48</v>
+      </c>
+      <c r="N17" s="75" t="n">
+        <f aca="false">SUM(B17:M17)</f>
+        <v>313.3</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B17,'Budget P&amp;L'!B15)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C17,'Budget P&amp;L'!C15)</f>
+        <v>435</v>
+      </c>
+      <c r="D18" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D17,'Budget P&amp;L'!D15)</f>
+        <v>435</v>
+      </c>
+      <c r="E18" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E17,'Budget P&amp;L'!E15)</f>
+        <v>435</v>
+      </c>
+      <c r="F18" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F17,'Budget P&amp;L'!F15)</f>
+        <v>870</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G17,'Budget P&amp;L'!G15)</f>
+        <v>435</v>
+      </c>
+      <c r="H18" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H17,'Budget P&amp;L'!H15)</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I17,'Budget P&amp;L'!I15)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J17,'Budget P&amp;L'!J15)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K17,'Budget P&amp;L'!K15)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L17,'Budget P&amp;L'!L15)</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M17,'Budget P&amp;L'!M15)</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="75" t="n">
+        <f aca="false">SUM(B18:M18)</f>
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="54" t="s">
+        <v>290</v>
+      </c>
+      <c r="B19" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B18,'Budget P&amp;L'!B16)</f>
+        <v>4320</v>
+      </c>
+      <c r="C19" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C18,'Budget P&amp;L'!C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D18,'Budget P&amp;L'!D16)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E18,'Budget P&amp;L'!E16)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F18,'Budget P&amp;L'!F16)</f>
+        <v>280</v>
+      </c>
+      <c r="G19" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G18,'Budget P&amp;L'!G16)</f>
+        <v>760</v>
+      </c>
+      <c r="H19" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H18,'Budget P&amp;L'!H16)</f>
+        <v>760</v>
+      </c>
+      <c r="I19" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I18,'Budget P&amp;L'!I16)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J18,'Budget P&amp;L'!J16)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K18,'Budget P&amp;L'!K16)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L18,'Budget P&amp;L'!L16)</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M18,'Budget P&amp;L'!M16)</f>
+        <v>0</v>
+      </c>
+      <c r="N19" s="75" t="n">
+        <f aca="false">SUM(B19:M19)</f>
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="54" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B20,'Budget P&amp;L'!B17)</f>
+        <v>18160.3</v>
+      </c>
+      <c r="C20" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C20,'Budget P&amp;L'!C17)</f>
+        <v>33566.6</v>
+      </c>
+      <c r="D20" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D20,'Budget P&amp;L'!D17)</f>
+        <v>37053.6</v>
+      </c>
+      <c r="E20" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E20,'Budget P&amp;L'!E17)</f>
+        <v>33728.59</v>
+      </c>
+      <c r="F20" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F20,'Budget P&amp;L'!F17)</f>
+        <v>46769.76</v>
+      </c>
+      <c r="G20" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G20,'Budget P&amp;L'!G17)</f>
+        <v>64034.11</v>
+      </c>
+      <c r="H20" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H20,'Budget P&amp;L'!H17)</f>
+        <v>91281.34</v>
+      </c>
+      <c r="I20" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I20,'Budget P&amp;L'!I17)</f>
+        <v>39314.1666666667</v>
+      </c>
+      <c r="J20" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J20,'Budget P&amp;L'!J17)</f>
+        <v>40074.1666666667</v>
+      </c>
+      <c r="K20" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K20,'Budget P&amp;L'!K17)</f>
+        <v>40074.1666666667</v>
+      </c>
+      <c r="L20" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L20,'Budget P&amp;L'!L17)</f>
+        <v>39314.1666666667</v>
+      </c>
+      <c r="M20" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M20,'Budget P&amp;L'!M17)</f>
+        <v>40834.1666666667</v>
+      </c>
+      <c r="N20" s="75" t="n">
+        <f aca="false">SUM(B20:M20)</f>
+        <v>524205.133333333</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54" t="s">
+        <v>291</v>
+      </c>
+      <c r="B21" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B19,'Budget P&amp;L'!B18)</f>
+        <v>2271.72</v>
+      </c>
+      <c r="C21" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C19,'Budget P&amp;L'!C18)</f>
+        <v>2808.37</v>
+      </c>
+      <c r="D21" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D19,'Budget P&amp;L'!D18)</f>
+        <v>2893.57</v>
+      </c>
+      <c r="E21" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E19,'Budget P&amp;L'!E18)</f>
+        <v>2750.47</v>
+      </c>
+      <c r="F21" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F19,'Budget P&amp;L'!F18)</f>
+        <v>3979.19</v>
+      </c>
+      <c r="G21" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G19,'Budget P&amp;L'!G18)</f>
+        <v>5164.66</v>
+      </c>
+      <c r="H21" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H19,'Budget P&amp;L'!H18)</f>
+        <v>7041.14</v>
+      </c>
+      <c r="I21" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I19,'Budget P&amp;L'!I18)</f>
+        <v>3097.73708333333</v>
+      </c>
+      <c r="J21" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J19,'Budget P&amp;L'!J18)</f>
+        <v>3097.73708333333</v>
+      </c>
+      <c r="K21" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K19,'Budget P&amp;L'!K18)</f>
+        <v>3097.73708333333</v>
+      </c>
+      <c r="L21" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L19,'Budget P&amp;L'!L18)</f>
+        <v>3097.73708333333</v>
+      </c>
+      <c r="M21" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M19,'Budget P&amp;L'!M18)</f>
+        <v>3097.73708333333</v>
+      </c>
+      <c r="N21" s="75" t="n">
+        <f aca="false">SUM(B21:M21)</f>
+        <v>42397.8054166667</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="54" t="s">
+        <v>293</v>
+      </c>
+      <c r="B22" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B21,'Budget P&amp;L'!B19)</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C21,'Budget P&amp;L'!C19)</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D21,'Budget P&amp;L'!D19)</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E21,'Budget P&amp;L'!E19)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F21,'Budget P&amp;L'!F19)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G21,'Budget P&amp;L'!G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H21,'Budget P&amp;L'!H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I21,'Budget P&amp;L'!I19)</f>
+        <v>2920</v>
+      </c>
+      <c r="J22" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J21,'Budget P&amp;L'!J19)</f>
+        <v>2920</v>
+      </c>
+      <c r="K22" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K21,'Budget P&amp;L'!K19)</f>
+        <v>2920</v>
+      </c>
+      <c r="L22" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L21,'Budget P&amp;L'!L19)</f>
+        <v>2920</v>
+      </c>
+      <c r="M22" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M21,'Budget P&amp;L'!M19)</f>
+        <v>2920</v>
+      </c>
+      <c r="N22" s="75" t="n">
+        <f aca="false">SUM(B22:M22)</f>
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="97" t="s">
+        <v>339</v>
+      </c>
+      <c r="B23" s="75" t="n">
+        <f aca="false">SUM(B16:B22)</f>
+        <v>26345.02</v>
+      </c>
+      <c r="C23" s="75" t="n">
+        <f aca="false">SUM(C16:C22)</f>
+        <v>37239.97</v>
+      </c>
+      <c r="D23" s="75" t="n">
+        <f aca="false">SUM(D16:D22)</f>
+        <v>40750.87</v>
+      </c>
+      <c r="E23" s="75" t="n">
+        <f aca="false">SUM(E16:E22)</f>
+        <v>38066.76</v>
+      </c>
+      <c r="F23" s="75" t="n">
+        <f aca="false">SUM(F16:F22)</f>
+        <v>51898.95</v>
+      </c>
+      <c r="G23" s="75" t="n">
+        <f aca="false">SUM(G16:G22)</f>
+        <v>70393.77</v>
+      </c>
+      <c r="H23" s="75" t="n">
+        <f aca="false">SUM(H16:H22)</f>
+        <v>99082.48</v>
+      </c>
+      <c r="I23" s="75" t="n">
+        <f aca="false">SUM(I16:I22)</f>
+        <v>49560.38375</v>
+      </c>
+      <c r="J23" s="75" t="n">
+        <f aca="false">SUM(J16:J22)</f>
+        <v>50320.38375</v>
+      </c>
+      <c r="K23" s="75" t="n">
+        <f aca="false">SUM(K16:K22)</f>
+        <v>50320.38375</v>
+      </c>
+      <c r="L23" s="75" t="n">
+        <f aca="false">SUM(L16:L22)</f>
+        <v>49560.38375</v>
+      </c>
+      <c r="M23" s="75" t="n">
+        <f aca="false">SUM(M16:M22)</f>
+        <v>51080.38375</v>
+      </c>
+      <c r="N23" s="75" t="n">
+        <f aca="false">SUM(N16:N22)</f>
+        <v>614619.73875</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="B24" s="78" t="n">
+        <f aca="false">B14-B23</f>
+        <v>38481.98</v>
+      </c>
+      <c r="C24" s="78" t="n">
+        <f aca="false">C14-C23</f>
+        <v>18578.78</v>
+      </c>
+      <c r="D24" s="78" t="n">
+        <f aca="false">D14-D23</f>
+        <v>62647.88</v>
+      </c>
+      <c r="E24" s="78" t="n">
+        <f aca="false">E14-E23</f>
+        <v>51397.49</v>
+      </c>
+      <c r="F24" s="78" t="n">
+        <f aca="false">F14-F23</f>
+        <v>48281.5</v>
+      </c>
+      <c r="G24" s="78" t="n">
+        <f aca="false">G14-G23</f>
+        <v>31730.23</v>
+      </c>
+      <c r="H24" s="78" t="n">
+        <f aca="false">H14-H23</f>
+        <v>77537.38</v>
+      </c>
+      <c r="I24" s="78" t="n">
+        <f aca="false">I14-I23</f>
+        <v>57790.1479960317</v>
+      </c>
+      <c r="J24" s="78" t="n">
+        <f aca="false">J14-J23</f>
+        <v>57030.1479960317</v>
+      </c>
+      <c r="K24" s="78" t="n">
+        <f aca="false">K14-K23</f>
+        <v>62912.3860912699</v>
+      </c>
+      <c r="L24" s="78" t="n">
+        <f aca="false">L14-L23</f>
+        <v>51907.9099007937</v>
+      </c>
+      <c r="M24" s="78" t="n">
+        <f aca="false">M14-M23</f>
+        <v>56270.1479960317</v>
+      </c>
+      <c r="N24" s="78" t="n">
+        <f aca="false">N14-N23</f>
+        <v>614565.979980159</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="53" t="s">
+        <v>341</v>
+      </c>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+      <c r="E25" s="51"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="51"/>
+      <c r="M25" s="51"/>
+      <c r="N25" s="51"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="B26" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,0,'Budget P&amp;L'!B24)</f>
+        <v>0</v>
+      </c>
+      <c r="C26" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,0,'Budget P&amp;L'!C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,0,'Budget P&amp;L'!D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,0,'Budget P&amp;L'!E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,0,'Budget P&amp;L'!F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,0,'Budget P&amp;L'!G24)</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,0,'Budget P&amp;L'!H24)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,0,'Budget P&amp;L'!I24)</f>
+        <v>7687.5</v>
+      </c>
+      <c r="J26" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,0,'Budget P&amp;L'!J24)</f>
+        <v>7687.5</v>
+      </c>
+      <c r="K26" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,0,'Budget P&amp;L'!K24)</f>
+        <v>7687.5</v>
+      </c>
+      <c r="L26" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,0,'Budget P&amp;L'!L24)</f>
+        <v>7687.5</v>
+      </c>
+      <c r="M26" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,0,'Budget P&amp;L'!M24)</f>
+        <v>7687.5</v>
+      </c>
+      <c r="N26" s="75" t="n">
+        <f aca="false">SUM(B26:M26)</f>
+        <v>38437.5</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="54" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,0,'Budget P&amp;L'!B25)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,0,'Budget P&amp;L'!C25)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,0,'Budget P&amp;L'!D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,0,'Budget P&amp;L'!E25)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,0,'Budget P&amp;L'!F25)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,0,'Budget P&amp;L'!G25)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,0,'Budget P&amp;L'!H25)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,0,'Budget P&amp;L'!I25)</f>
+        <v>5666.66666666667</v>
+      </c>
+      <c r="J27" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,0,'Budget P&amp;L'!J25)</f>
+        <v>5666.66666666667</v>
+      </c>
+      <c r="K27" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,0,'Budget P&amp;L'!K25)</f>
+        <v>5666.66666666667</v>
+      </c>
+      <c r="L27" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,0,'Budget P&amp;L'!L25)</f>
+        <v>5666.66666666667</v>
+      </c>
+      <c r="M27" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,0,'Budget P&amp;L'!M25)</f>
+        <v>5666.66666666667</v>
+      </c>
+      <c r="N27" s="75" t="n">
+        <f aca="false">SUM(B27:M27)</f>
+        <v>28333.3333333333</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="B28" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,0,'Budget P&amp;L'!B26)</f>
+        <v>0</v>
+      </c>
+      <c r="C28" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,0,'Budget P&amp;L'!C26)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,0,'Budget P&amp;L'!D26)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,0,'Budget P&amp;L'!E26)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,0,'Budget P&amp;L'!F26)</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,0,'Budget P&amp;L'!G26)</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,0,'Budget P&amp;L'!H26)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,0,'Budget P&amp;L'!I26)</f>
+        <v>1038.82875</v>
+      </c>
+      <c r="J28" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,0,'Budget P&amp;L'!J26)</f>
+        <v>1038.82875</v>
+      </c>
+      <c r="K28" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,0,'Budget P&amp;L'!K26)</f>
+        <v>1038.82875</v>
+      </c>
+      <c r="L28" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,0,'Budget P&amp;L'!L26)</f>
+        <v>1038.82875</v>
+      </c>
+      <c r="M28" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,0,'Budget P&amp;L'!M26)</f>
+        <v>1038.82875</v>
+      </c>
+      <c r="N28" s="75" t="n">
+        <f aca="false">SUM(B28:M28)</f>
+        <v>5194.14375</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,0,'Budget P&amp;L'!B27)</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,0,'Budget P&amp;L'!C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,0,'Budget P&amp;L'!D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,0,'Budget P&amp;L'!E27)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,0,'Budget P&amp;L'!F27)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,0,'Budget P&amp;L'!G27)</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,0,'Budget P&amp;L'!H27)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,0,'Budget P&amp;L'!I27)</f>
+        <v>1080</v>
+      </c>
+      <c r="J29" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,0,'Budget P&amp;L'!J27)</f>
+        <v>1080</v>
+      </c>
+      <c r="K29" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,0,'Budget P&amp;L'!K27)</f>
+        <v>1080</v>
+      </c>
+      <c r="L29" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,0,'Budget P&amp;L'!L27)</f>
+        <v>1080</v>
+      </c>
+      <c r="M29" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,0,'Budget P&amp;L'!M27)</f>
+        <v>1080</v>
+      </c>
+      <c r="N29" s="75" t="n">
+        <f aca="false">SUM(B29:M29)</f>
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="B30" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B25,'Budget P&amp;L'!B28)</f>
+        <v>0</v>
+      </c>
+      <c r="C30" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C25,'Budget P&amp;L'!C28)</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D25,'Budget P&amp;L'!D28)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E25,'Budget P&amp;L'!E28)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F25,'Budget P&amp;L'!F28)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G25,'Budget P&amp;L'!G28)</f>
+        <v>338</v>
+      </c>
+      <c r="H30" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H25,'Budget P&amp;L'!H28)</f>
+        <v>590.36</v>
+      </c>
+      <c r="I30" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I25,'Budget P&amp;L'!I28)</f>
+        <v>56.33</v>
+      </c>
+      <c r="J30" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J25,'Budget P&amp;L'!J28)</f>
+        <v>56.33</v>
+      </c>
+      <c r="K30" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K25,'Budget P&amp;L'!K28)</f>
+        <v>56.33</v>
+      </c>
+      <c r="L30" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L25,'Budget P&amp;L'!L28)</f>
+        <v>56.33</v>
+      </c>
+      <c r="M30" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M25,'Budget P&amp;L'!M28)</f>
+        <v>56.33</v>
+      </c>
+      <c r="N30" s="75" t="n">
+        <f aca="false">SUM(B30:M30)</f>
+        <v>1210.01</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="B31" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B26,'Budget P&amp;L'!B29)</f>
+        <v>9.6</v>
+      </c>
+      <c r="C31" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C26,'Budget P&amp;L'!C29)</f>
+        <v>5</v>
+      </c>
+      <c r="D31" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D26,'Budget P&amp;L'!D29)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E26,'Budget P&amp;L'!E29)</f>
+        <v>48.99</v>
+      </c>
+      <c r="F31" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F26,'Budget P&amp;L'!F29)</f>
+        <v>71.42</v>
+      </c>
+      <c r="G31" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G26,'Budget P&amp;L'!G29)</f>
+        <v>73.52</v>
+      </c>
+      <c r="H31" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H26,'Budget P&amp;L'!H29)</f>
+        <v>68.63</v>
+      </c>
+      <c r="I31" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I26,'Budget P&amp;L'!I29)</f>
+        <v>35.42</v>
+      </c>
+      <c r="J31" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J26,'Budget P&amp;L'!J29)</f>
+        <v>35.42</v>
+      </c>
+      <c r="K31" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K26,'Budget P&amp;L'!K29)</f>
+        <v>35.42</v>
+      </c>
+      <c r="L31" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L26,'Budget P&amp;L'!L29)</f>
+        <v>35.42</v>
+      </c>
+      <c r="M31" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M26,'Budget P&amp;L'!M29)</f>
+        <v>35.42</v>
+      </c>
+      <c r="N31" s="75" t="n">
+        <f aca="false">SUM(B31:M31)</f>
+        <v>458.26</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="B32" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B27,'Budget P&amp;L'!B30)</f>
+        <v>100</v>
+      </c>
+      <c r="C32" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C27,'Budget P&amp;L'!C30)</f>
+        <v>100</v>
+      </c>
+      <c r="D32" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D27,'Budget P&amp;L'!D30)</f>
+        <v>100</v>
+      </c>
+      <c r="E32" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E27,'Budget P&amp;L'!E30)</f>
+        <v>100</v>
+      </c>
+      <c r="F32" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F27,'Budget P&amp;L'!F30)</f>
+        <v>185</v>
+      </c>
+      <c r="G32" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G27,'Budget P&amp;L'!G30)</f>
+        <v>122.99</v>
+      </c>
+      <c r="H32" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H27,'Budget P&amp;L'!H30)</f>
+        <v>252.57</v>
+      </c>
+      <c r="I32" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I27,'Budget P&amp;L'!I30)</f>
+        <v>118</v>
+      </c>
+      <c r="J32" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J27,'Budget P&amp;L'!J30)</f>
+        <v>118</v>
+      </c>
+      <c r="K32" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K27,'Budget P&amp;L'!K30)</f>
+        <v>118</v>
+      </c>
+      <c r="L32" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L27,'Budget P&amp;L'!L30)</f>
+        <v>118</v>
+      </c>
+      <c r="M32" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M27,'Budget P&amp;L'!M30)</f>
+        <v>118</v>
+      </c>
+      <c r="N32" s="75" t="n">
+        <f aca="false">SUM(B32:M32)</f>
+        <v>1550.56</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="54" t="s">
+        <v>263</v>
+      </c>
+      <c r="B33" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B28,'Budget P&amp;L'!B31)</f>
+        <v>148.98</v>
+      </c>
+      <c r="C33" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C28,'Budget P&amp;L'!C31)</f>
+        <v>163.14</v>
+      </c>
+      <c r="D33" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D28,'Budget P&amp;L'!D31)</f>
+        <v>203.88</v>
+      </c>
+      <c r="E33" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E28,'Budget P&amp;L'!E31)</f>
+        <v>171.34</v>
+      </c>
+      <c r="F33" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F28,'Budget P&amp;L'!F31)</f>
+        <v>168.44</v>
+      </c>
+      <c r="G33" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G28,'Budget P&amp;L'!G31)</f>
+        <v>174.18</v>
+      </c>
+      <c r="H33" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H28,'Budget P&amp;L'!H31)</f>
+        <v>194.18</v>
+      </c>
+      <c r="I33" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I28,'Budget P&amp;L'!I31)</f>
+        <v>171.66</v>
+      </c>
+      <c r="J33" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J28,'Budget P&amp;L'!J31)</f>
+        <v>171.66</v>
+      </c>
+      <c r="K33" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K28,'Budget P&amp;L'!K31)</f>
+        <v>171.66</v>
+      </c>
+      <c r="L33" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L28,'Budget P&amp;L'!L31)</f>
+        <v>171.66</v>
+      </c>
+      <c r="M33" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M28,'Budget P&amp;L'!M31)</f>
+        <v>171.66</v>
+      </c>
+      <c r="N33" s="75" t="n">
+        <f aca="false">SUM(B33:M33)</f>
+        <v>2082.44</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="B34" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B29,'Budget P&amp;L'!B32)</f>
+        <v>0</v>
+      </c>
+      <c r="C34" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C29,'Budget P&amp;L'!C32)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D29,'Budget P&amp;L'!D32)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E29,'Budget P&amp;L'!E32)</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F29,'Budget P&amp;L'!F32)</f>
+        <v>0</v>
+      </c>
+      <c r="G34" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G29,'Budget P&amp;L'!G32)</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H29,'Budget P&amp;L'!H32)</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I29,'Budget P&amp;L'!I32)</f>
+        <v>1150</v>
+      </c>
+      <c r="J34" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J29,'Budget P&amp;L'!J32)</f>
+        <v>1150</v>
+      </c>
+      <c r="K34" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K29,'Budget P&amp;L'!K32)</f>
+        <v>1150</v>
+      </c>
+      <c r="L34" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L29,'Budget P&amp;L'!L32)</f>
+        <v>1150</v>
+      </c>
+      <c r="M34" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M29,'Budget P&amp;L'!M32)</f>
+        <v>1150</v>
+      </c>
+      <c r="N34" s="75" t="n">
+        <f aca="false">SUM(B34:M34)</f>
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="B35" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B30,'Budget P&amp;L'!B33)</f>
+        <v>399.75</v>
+      </c>
+      <c r="C35" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C30,'Budget P&amp;L'!C33)</f>
+        <v>293.25</v>
+      </c>
+      <c r="D35" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D30,'Budget P&amp;L'!D33)</f>
+        <v>1471.25</v>
+      </c>
+      <c r="E35" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E30,'Budget P&amp;L'!E33)</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F30,'Budget P&amp;L'!F33)</f>
+        <v>3419.63</v>
+      </c>
+      <c r="G35" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G30,'Budget P&amp;L'!G33)</f>
+        <v>5300</v>
+      </c>
+      <c r="H35" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H30,'Budget P&amp;L'!H33)</f>
+        <v>5200</v>
+      </c>
+      <c r="I35" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I30,'Budget P&amp;L'!I33)</f>
+        <v>1813.98</v>
+      </c>
+      <c r="J35" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J30,'Budget P&amp;L'!J33)</f>
+        <v>1813.98</v>
+      </c>
+      <c r="K35" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K30,'Budget P&amp;L'!K33)</f>
+        <v>1813.98</v>
+      </c>
+      <c r="L35" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L30,'Budget P&amp;L'!L33)</f>
+        <v>1813.98</v>
+      </c>
+      <c r="M35" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M30,'Budget P&amp;L'!M33)</f>
+        <v>1813.98</v>
+      </c>
+      <c r="N35" s="75" t="n">
+        <f aca="false">SUM(B35:M35)</f>
+        <v>25153.78</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="B36" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B31,'Budget P&amp;L'!B34)</f>
+        <v>539.3</v>
+      </c>
+      <c r="C36" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C31,'Budget P&amp;L'!C34)</f>
+        <v>439.55</v>
+      </c>
+      <c r="D36" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D31,'Budget P&amp;L'!D34)</f>
+        <v>319.77</v>
+      </c>
+      <c r="E36" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E31,'Budget P&amp;L'!E34)</f>
+        <v>486.47</v>
+      </c>
+      <c r="F36" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F31,'Budget P&amp;L'!F34)</f>
+        <v>579.59</v>
+      </c>
+      <c r="G36" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G31,'Budget P&amp;L'!G34)</f>
+        <v>160.62</v>
+      </c>
+      <c r="H36" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H31,'Budget P&amp;L'!H34)</f>
+        <v>202.85</v>
+      </c>
+      <c r="I36" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I31,'Budget P&amp;L'!I34)</f>
+        <v>420.88</v>
+      </c>
+      <c r="J36" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J31,'Budget P&amp;L'!J34)</f>
+        <v>420.88</v>
+      </c>
+      <c r="K36" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K31,'Budget P&amp;L'!K34)</f>
+        <v>420.88</v>
+      </c>
+      <c r="L36" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L31,'Budget P&amp;L'!L34)</f>
+        <v>420.88</v>
+      </c>
+      <c r="M36" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M31,'Budget P&amp;L'!M34)</f>
+        <v>420.88</v>
+      </c>
+      <c r="N36" s="75" t="n">
+        <f aca="false">SUM(B36:M36)</f>
+        <v>4832.55</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B37" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B32,'Budget P&amp;L'!B35)</f>
+        <v>2705.65</v>
+      </c>
+      <c r="C37" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C32,'Budget P&amp;L'!C35)</f>
+        <v>1598.23</v>
+      </c>
+      <c r="D37" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D32,'Budget P&amp;L'!D35)</f>
+        <v>2648.42</v>
+      </c>
+      <c r="E37" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E32,'Budget P&amp;L'!E35)</f>
+        <v>3059.94</v>
+      </c>
+      <c r="F37" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F32,'Budget P&amp;L'!F35)</f>
+        <v>1942.95</v>
+      </c>
+      <c r="G37" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G32,'Budget P&amp;L'!G35)</f>
+        <v>2497.17</v>
+      </c>
+      <c r="H37" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H32,'Budget P&amp;L'!H35)</f>
+        <v>3145.14</v>
+      </c>
+      <c r="I37" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I32,'Budget P&amp;L'!I35)</f>
+        <v>2408.73</v>
+      </c>
+      <c r="J37" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J32,'Budget P&amp;L'!J35)</f>
+        <v>2408.73</v>
+      </c>
+      <c r="K37" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K32,'Budget P&amp;L'!K35)</f>
+        <v>2408.73</v>
+      </c>
+      <c r="L37" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L32,'Budget P&amp;L'!L35)</f>
+        <v>2408.73</v>
+      </c>
+      <c r="M37" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M32,'Budget P&amp;L'!M35)</f>
+        <v>2408.73</v>
+      </c>
+      <c r="N37" s="75" t="n">
+        <f aca="false">SUM(B37:M37)</f>
+        <v>29641.15</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54" t="s">
+        <v>296</v>
+      </c>
+      <c r="B38" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B33,0)</f>
+        <v>1630</v>
+      </c>
+      <c r="C38" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C33,0)</f>
+        <v>340</v>
+      </c>
+      <c r="D38" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D33,0)</f>
+        <v>280</v>
+      </c>
+      <c r="E38" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E33,0)</f>
+        <v>1790</v>
+      </c>
+      <c r="F38" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F33,0)</f>
+        <v>4096</v>
+      </c>
+      <c r="G38" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G33,0)</f>
+        <v>280</v>
+      </c>
+      <c r="H38" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M38" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M33,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N38" s="75" t="n">
+        <f aca="false">SUM(B38:M38)</f>
+        <v>8416</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="54" t="s">
+        <v>268</v>
+      </c>
+      <c r="B39" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B34,'Budget P&amp;L'!B36)</f>
+        <v>162.91</v>
+      </c>
+      <c r="C39" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C34,'Budget P&amp;L'!C36)</f>
+        <v>244.59</v>
+      </c>
+      <c r="D39" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D34,'Budget P&amp;L'!D36)</f>
+        <v>295.51</v>
+      </c>
+      <c r="E39" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E34,'Budget P&amp;L'!E36)</f>
+        <v>91.12</v>
+      </c>
+      <c r="F39" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F34,'Budget P&amp;L'!F36)</f>
+        <v>222.15</v>
+      </c>
+      <c r="G39" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G34,'Budget P&amp;L'!G36)</f>
+        <v>328.8</v>
+      </c>
+      <c r="H39" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H34,'Budget P&amp;L'!H36)</f>
+        <v>404.14</v>
+      </c>
+      <c r="I39" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I34,'Budget P&amp;L'!I36)</f>
+        <v>224.18</v>
+      </c>
+      <c r="J39" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J34,'Budget P&amp;L'!J36)</f>
+        <v>224.18</v>
+      </c>
+      <c r="K39" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K34,'Budget P&amp;L'!K36)</f>
+        <v>224.18</v>
+      </c>
+      <c r="L39" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L34,'Budget P&amp;L'!L36)</f>
+        <v>224.18</v>
+      </c>
+      <c r="M39" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M34,'Budget P&amp;L'!M36)</f>
+        <v>224.18</v>
+      </c>
+      <c r="N39" s="75" t="n">
+        <f aca="false">SUM(B39:M39)</f>
+        <v>2870.12</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="B40" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B35,'Budget P&amp;L'!B37)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C35,'Budget P&amp;L'!C37)</f>
+        <v>12</v>
+      </c>
+      <c r="D40" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D35,'Budget P&amp;L'!D37)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E35,'Budget P&amp;L'!E37)</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F35,'Budget P&amp;L'!F37)</f>
+        <v>55.35</v>
+      </c>
+      <c r="G40" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G35,'Budget P&amp;L'!G37)</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H35,'Budget P&amp;L'!H37)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I35,'Budget P&amp;L'!I37)</f>
+        <v>11.22</v>
+      </c>
+      <c r="J40" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J35,'Budget P&amp;L'!J37)</f>
+        <v>11.22</v>
+      </c>
+      <c r="K40" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K35,'Budget P&amp;L'!K37)</f>
+        <v>11.22</v>
+      </c>
+      <c r="L40" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L35,'Budget P&amp;L'!L37)</f>
+        <v>11.22</v>
+      </c>
+      <c r="M40" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M35,'Budget P&amp;L'!M37)</f>
+        <v>11.22</v>
+      </c>
+      <c r="N40" s="75" t="n">
+        <f aca="false">SUM(B40:M40)</f>
+        <v>123.45</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="B41" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B36,'Budget P&amp;L'!B38)</f>
+        <v>1200</v>
+      </c>
+      <c r="C41" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C36,'Budget P&amp;L'!C38)</f>
+        <v>1200</v>
+      </c>
+      <c r="D41" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D36,'Budget P&amp;L'!D38)</f>
+        <v>1200</v>
+      </c>
+      <c r="E41" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E36,'Budget P&amp;L'!E38)</f>
+        <v>1200</v>
+      </c>
+      <c r="F41" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F36,'Budget P&amp;L'!F38)</f>
+        <v>1200</v>
+      </c>
+      <c r="G41" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G36,'Budget P&amp;L'!G38)</f>
+        <v>1200</v>
+      </c>
+      <c r="H41" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H36,'Budget P&amp;L'!H38)</f>
+        <v>1200</v>
+      </c>
+      <c r="I41" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I36,'Budget P&amp;L'!I38)</f>
+        <v>1200</v>
+      </c>
+      <c r="J41" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J36,'Budget P&amp;L'!J38)</f>
+        <v>1200</v>
+      </c>
+      <c r="K41" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K36,'Budget P&amp;L'!K38)</f>
+        <v>1200</v>
+      </c>
+      <c r="L41" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L36,'Budget P&amp;L'!L38)</f>
+        <v>1200</v>
+      </c>
+      <c r="M41" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M36,'Budget P&amp;L'!M38)</f>
+        <v>1200</v>
+      </c>
+      <c r="N41" s="75" t="n">
+        <f aca="false">SUM(B41:M41)</f>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="54" t="s">
+        <v>297</v>
+      </c>
+      <c r="B42" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M37,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N42" s="75" t="n">
+        <f aca="false">SUM(B42:M42)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" s="74" t="n">
+        <f aca="false">IF(1&lt;=$B$5,'Budget vs Actual'!B38,'Budget P&amp;L'!B39)</f>
+        <v>0</v>
+      </c>
+      <c r="C43" s="74" t="n">
+        <f aca="false">IF(2&lt;=$B$5,'Budget vs Actual'!C38,'Budget P&amp;L'!C39)</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="74" t="n">
+        <f aca="false">IF(3&lt;=$B$5,'Budget vs Actual'!D38,'Budget P&amp;L'!D39)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="74" t="n">
+        <f aca="false">IF(4&lt;=$B$5,'Budget vs Actual'!E38,'Budget P&amp;L'!E39)</f>
+        <v>207.36</v>
+      </c>
+      <c r="F43" s="74" t="n">
+        <f aca="false">IF(5&lt;=$B$5,'Budget vs Actual'!F38,'Budget P&amp;L'!F39)</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="74" t="n">
+        <f aca="false">IF(6&lt;=$B$5,'Budget vs Actual'!G38,'Budget P&amp;L'!G39)</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="74" t="n">
+        <f aca="false">IF(7&lt;=$B$5,'Budget vs Actual'!H38,'Budget P&amp;L'!H39)</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="74" t="n">
+        <f aca="false">IF(8&lt;=$B$5,'Budget vs Actual'!I38,'Budget P&amp;L'!I39)</f>
+        <v>34.56</v>
+      </c>
+      <c r="J43" s="74" t="n">
+        <f aca="false">IF(9&lt;=$B$5,'Budget vs Actual'!J38,'Budget P&amp;L'!J39)</f>
+        <v>34.56</v>
+      </c>
+      <c r="K43" s="74" t="n">
+        <f aca="false">IF(10&lt;=$B$5,'Budget vs Actual'!K38,'Budget P&amp;L'!K39)</f>
+        <v>34.56</v>
+      </c>
+      <c r="L43" s="74" t="n">
+        <f aca="false">IF(11&lt;=$B$5,'Budget vs Actual'!L38,'Budget P&amp;L'!L39)</f>
+        <v>34.56</v>
+      </c>
+      <c r="M43" s="74" t="n">
+        <f aca="false">IF(12&lt;=$B$5,'Budget vs Actual'!M38,'Budget P&amp;L'!M39)</f>
+        <v>34.56</v>
+      </c>
+      <c r="N43" s="75" t="n">
+        <f aca="false">SUM(B43:M43)</f>
+        <v>380.16</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="97" t="s">
+        <v>298</v>
+      </c>
+      <c r="B44" s="75" t="n">
+        <f aca="false">SUM(B26:B43)</f>
+        <v>6896.19</v>
+      </c>
+      <c r="C44" s="75" t="n">
+        <f aca="false">SUM(C26:C43)</f>
+        <v>4395.76</v>
+      </c>
+      <c r="D44" s="75" t="n">
+        <f aca="false">SUM(D26:D43)</f>
+        <v>6522.83</v>
+      </c>
+      <c r="E44" s="75" t="n">
+        <f aca="false">SUM(E26:E43)</f>
+        <v>7155.22</v>
+      </c>
+      <c r="F44" s="75" t="n">
+        <f aca="false">SUM(F26:F43)</f>
+        <v>11940.53</v>
+      </c>
+      <c r="G44" s="75" t="n">
+        <f aca="false">SUM(G26:G43)</f>
+        <v>10475.28</v>
+      </c>
+      <c r="H44" s="75" t="n">
+        <f aca="false">SUM(H26:H43)</f>
+        <v>11257.87</v>
+      </c>
+      <c r="I44" s="75" t="n">
+        <f aca="false">SUM(I26:I43)</f>
+        <v>23117.9554166667</v>
+      </c>
+      <c r="J44" s="75" t="n">
+        <f aca="false">SUM(J26:J43)</f>
+        <v>23117.9554166667</v>
+      </c>
+      <c r="K44" s="75" t="n">
+        <f aca="false">SUM(K26:K43)</f>
+        <v>23117.9554166667</v>
+      </c>
+      <c r="L44" s="75" t="n">
+        <f aca="false">SUM(L26:L43)</f>
+        <v>23117.9554166667</v>
+      </c>
+      <c r="M44" s="75" t="n">
+        <f aca="false">SUM(M26:M43)</f>
+        <v>23117.9554166667</v>
+      </c>
+      <c r="N44" s="75" t="n">
+        <f aca="false">SUM(N26:N43)</f>
+        <v>174233.457083333</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="118" t="s">
+        <v>306</v>
+      </c>
+      <c r="B45" s="119" t="n">
+        <f aca="false">B24-B44</f>
+        <v>31585.79</v>
+      </c>
+      <c r="C45" s="119" t="n">
+        <f aca="false">C24-C44</f>
+        <v>14183.02</v>
+      </c>
+      <c r="D45" s="119" t="n">
+        <f aca="false">D24-D44</f>
+        <v>56125.05</v>
+      </c>
+      <c r="E45" s="119" t="n">
+        <f aca="false">E24-E44</f>
+        <v>44242.27</v>
+      </c>
+      <c r="F45" s="119" t="n">
+        <f aca="false">F24-F44</f>
+        <v>36340.97</v>
+      </c>
+      <c r="G45" s="119" t="n">
+        <f aca="false">G24-G44</f>
+        <v>21254.95</v>
+      </c>
+      <c r="H45" s="119" t="n">
+        <f aca="false">H24-H44</f>
+        <v>66279.51</v>
+      </c>
+      <c r="I45" s="119" t="n">
+        <f aca="false">I24-I44</f>
+        <v>34672.1925793651</v>
+      </c>
+      <c r="J45" s="119" t="n">
+        <f aca="false">J24-J44</f>
+        <v>33912.1925793651</v>
+      </c>
+      <c r="K45" s="119" t="n">
+        <f aca="false">K24-K44</f>
+        <v>39794.4306746032</v>
+      </c>
+      <c r="L45" s="119" t="n">
+        <f aca="false">L24-L44</f>
+        <v>28789.954484127</v>
+      </c>
+      <c r="M45" s="119" t="n">
+        <f aca="false">M24-M44</f>
+        <v>33152.1925793651</v>
+      </c>
+      <c r="N45" s="119" t="n">
+        <f aca="false">N24-N44</f>
+        <v>440332.522896826</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="B46" s="120" t="n">
+        <f aca="false">IF(B14=0,0,B45/B14)</f>
+        <v>0.487232017523563</v>
+      </c>
+      <c r="C46" s="120" t="n">
+        <f aca="false">IF(C14=0,0,C45/C14)</f>
+        <v>0.254090605755235</v>
+      </c>
+      <c r="D46" s="120" t="n">
+        <f aca="false">IF(D14=0,0,D45/D14)</f>
+        <v>0.542802016465383</v>
+      </c>
+      <c r="E46" s="120" t="n">
+        <f aca="false">IF(E14=0,0,E45/E14)</f>
+        <v>0.4945245726645</v>
+      </c>
+      <c r="F46" s="120" t="n">
+        <f aca="false">IF(F14=0,0,F45/F14)</f>
+        <v>0.36275510840688</v>
+      </c>
+      <c r="G46" s="120" t="n">
+        <f aca="false">IF(G14=0,0,G45/G14)</f>
+        <v>0.208128843366887</v>
+      </c>
+      <c r="H46" s="120" t="n">
+        <f aca="false">IF(H14=0,0,H45/H14)</f>
+        <v>0.37526646210681</v>
+      </c>
+      <c r="I46" s="120" t="n">
+        <f aca="false">IF(I14=0,0,I45/I14)</f>
+        <v>0.322981097675343</v>
+      </c>
+      <c r="J46" s="120" t="n">
+        <f aca="false">IF(J14=0,0,J45/J14)</f>
+        <v>0.315901486725692</v>
+      </c>
+      <c r="K46" s="120" t="n">
+        <f aca="false">IF(K14=0,0,K45/K14)</f>
+        <v>0.351439170218897</v>
+      </c>
+      <c r="L46" s="120" t="n">
+        <f aca="false">IF(L14=0,0,L45/L14)</f>
+        <v>0.283733503819514</v>
+      </c>
+      <c r="M46" s="120" t="n">
+        <f aca="false">IF(M14=0,0,M45/M14)</f>
+        <v>0.308821875776042</v>
+      </c>
+      <c r="N46" s="120" t="n">
+        <f aca="false">IF(N14=0,0,N45/N14)</f>
+        <v>0.358231076221518</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="53" t="s">
+        <v>343</v>
+      </c>
+      <c r="B48" s="51"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="51"/>
+      <c r="K48" s="51"/>
+      <c r="L48" s="51"/>
+      <c r="M48" s="51"/>
+      <c r="N48" s="51"/>
+    </row>
+    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="108" t="s">
+        <v>344</v>
+      </c>
+      <c r="B49" s="108"/>
+      <c r="C49" s="108"/>
+      <c r="D49" s="108"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="108"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="108"/>
+      <c r="J49" s="108"/>
+      <c r="K49" s="108"/>
+      <c r="L49" s="108"/>
+      <c r="M49" s="108"/>
+      <c r="N49" s="108"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="N50" s="121" t="n">
+        <f aca="false">N45</f>
+        <v>440332.522896826</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="54" t="s">
+        <v>346</v>
+      </c>
+      <c r="N51" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$24:INDEX('Budget P&amp;L'!$B$24:$M$24,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-53812.5</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="54" t="s">
+        <v>347</v>
+      </c>
+      <c r="N52" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$25:INDEX('Budget P&amp;L'!$B$25:$M$25,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-39666.6666666667</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="54" t="s">
+        <v>348</v>
+      </c>
+      <c r="N53" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$26:INDEX('Budget P&amp;L'!$B$26:$M$26,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-7271.80125</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="54" t="s">
+        <v>349</v>
+      </c>
+      <c r="N54" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$27:INDEX('Budget P&amp;L'!$B$27:$M$27,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-7560</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="54" t="s">
+        <v>350</v>
+      </c>
+      <c r="N55" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$19:INDEX('Budget P&amp;L'!$B$19:$M$19,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-20440</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="54" t="s">
+        <v>351</v>
+      </c>
+      <c r="N56" s="122" t="n">
+        <f aca="false">-SUM('Budget P&amp;L'!$B$32:INDEX('Budget P&amp;L'!$B$32:$M$32,1,MAX($B$5,1)))*($B$5&gt;0)</f>
+        <v>-8050</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="N57" s="77" t="n">
+        <f aca="false">N50+SUM(N51:N56)</f>
+        <v>303531.554980159</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="108" t="s">
+        <v>353</v>
+      </c>
+      <c r="B59" s="108"/>
+      <c r="C59" s="108"/>
+      <c r="D59" s="108"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="108"/>
+      <c r="G59" s="108"/>
+      <c r="H59" s="108"/>
+      <c r="I59" s="108"/>
+      <c r="J59" s="108"/>
+      <c r="K59" s="108"/>
+      <c r="L59" s="108"/>
+      <c r="M59" s="108"/>
+      <c r="N59" s="108"/>
+    </row>
+    <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="108" t="s">
+        <v>354</v>
+      </c>
+      <c r="B60" s="108"/>
+      <c r="C60" s="108"/>
+      <c r="D60" s="108"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="108"/>
+      <c r="G60" s="108"/>
+      <c r="H60" s="108"/>
+      <c r="I60" s="108"/>
+      <c r="J60" s="108"/>
+      <c r="K60" s="108"/>
+      <c r="L60" s="108"/>
+      <c r="M60" s="108"/>
+      <c r="N60" s="108"/>
+    </row>
+    <row r="61" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="108" t="s">
+        <v>355</v>
+      </c>
+      <c r="B61" s="108"/>
+      <c r="C61" s="108"/>
+      <c r="D61" s="108"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="108"/>
+      <c r="G61" s="108"/>
+      <c r="H61" s="108"/>
+      <c r="I61" s="108"/>
+      <c r="J61" s="108"/>
+      <c r="K61" s="108"/>
+      <c r="L61" s="108"/>
+      <c r="M61" s="108"/>
+      <c r="N61" s="108"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A49:N49"/>
+    <mergeCell ref="A59:N59"/>
+    <mergeCell ref="A60:N60"/>
+    <mergeCell ref="A61:N61"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B9:M9">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>"ACTUAL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>"BUDGET"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:D44"/>
+  <dimension ref="B2:D60"/>
   <sheetFormatPr defaultColWidth="8.55859375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
@@ -9487,362 +12745,472 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="123" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="3" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="53" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-    </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="58" t="s">
-        <v>327</v>
-      </c>
-      <c r="C7" s="110" t="s">
-        <v>328</v>
-      </c>
-      <c r="D7" s="110"/>
-    </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="58" t="s">
-        <v>329</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>330</v>
-      </c>
-      <c r="D8" s="110"/>
-    </row>
-    <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="58" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="110" t="s">
-        <v>332</v>
-      </c>
-      <c r="D9" s="110"/>
-    </row>
-    <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="58" t="s">
-        <v>333</v>
-      </c>
-      <c r="C10" s="110" t="s">
-        <v>334</v>
-      </c>
-      <c r="D10" s="110"/>
-    </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="58" t="s">
-        <v>335</v>
-      </c>
-      <c r="C11" s="110" t="s">
-        <v>336</v>
-      </c>
-      <c r="D11" s="110"/>
-    </row>
-    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="58" t="s">
-        <v>337</v>
-      </c>
-      <c r="C12" s="110" t="s">
-        <v>338</v>
-      </c>
-      <c r="D12" s="110"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="53" t="s">
-        <v>339</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="111" t="s">
-        <v>340</v>
-      </c>
-      <c r="C15" s="54" t="s">
-        <v>341</v>
-      </c>
-      <c r="D15" s="54"/>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="112" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="124" t="s">
+        <v>358</v>
+      </c>
+      <c r="C6" s="125"/>
+      <c r="D6" s="125"/>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="126" t="s">
+        <v>359</v>
+      </c>
+      <c r="C7" s="127" t="s">
+        <v>360</v>
+      </c>
+      <c r="D7" s="127"/>
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="128" t="s">
+        <v>361</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>362</v>
+      </c>
+      <c r="D8" s="127"/>
+    </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="128" t="s">
+        <v>363</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="127"/>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="124" t="s">
+        <v>365</v>
+      </c>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="128" t="s">
+        <v>366</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>367</v>
+      </c>
+      <c r="D12" s="127"/>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="128" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="127" t="s">
+        <v>369</v>
+      </c>
+      <c r="D13" s="127"/>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="128" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="127" t="s">
+        <v>371</v>
+      </c>
+      <c r="D14" s="127"/>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="128" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="127" t="s">
+        <v>373</v>
+      </c>
+      <c r="D15" s="127"/>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="128" t="s">
+        <v>374</v>
+      </c>
+      <c r="C16" s="127" t="s">
+        <v>375</v>
+      </c>
+      <c r="D16" s="127"/>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="128" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" s="127" t="s">
+        <v>377</v>
+      </c>
+      <c r="D17" s="127"/>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="128" t="s">
+        <v>378</v>
+      </c>
+      <c r="C18" s="127" t="s">
+        <v>379</v>
+      </c>
+      <c r="D18" s="127"/>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="129"/>
+      <c r="C19" s="129"/>
+      <c r="D19" s="130"/>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="124" t="s">
+        <v>380</v>
+      </c>
+      <c r="C20" s="125"/>
+      <c r="D20" s="131"/>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="132" t="s">
+        <v>381</v>
+      </c>
+      <c r="C21" s="129" t="s">
+        <v>382</v>
+      </c>
+      <c r="D21" s="133"/>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="126" t="s">
+        <v>383</v>
+      </c>
+      <c r="C22" s="129" t="s">
+        <v>384</v>
+      </c>
+      <c r="D22" s="130"/>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="128" t="s">
+        <v>385</v>
+      </c>
+      <c r="C23" s="129" t="s">
+        <v>386</v>
+      </c>
+      <c r="D23" s="130"/>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="134" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="129" t="s">
+        <v>388</v>
+      </c>
+      <c r="D24" s="133"/>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="135" t="s">
+        <v>389</v>
+      </c>
+      <c r="C25" s="129" t="s">
+        <v>390</v>
+      </c>
+      <c r="D25" s="130"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="129"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="129"/>
+    </row>
+    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="124" t="s">
+        <v>391</v>
+      </c>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="129" t="s">
+        <v>392</v>
+      </c>
+      <c r="C28" s="129"/>
+      <c r="D28" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$14</f>
+        <v>1229185.71873016</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="129" t="s">
+        <v>294</v>
+      </c>
+      <c r="C29" s="129"/>
+      <c r="D29" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$23</f>
+        <v>614619.73875</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="129" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" s="129"/>
+      <c r="D30" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$24</f>
+        <v>614565.979980159</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="129" t="s">
+        <v>394</v>
+      </c>
+      <c r="C31" s="129"/>
+      <c r="D31" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$44</f>
+        <v>174233.457083333</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="128" t="s">
+        <v>395</v>
+      </c>
+      <c r="C32" s="129"/>
+      <c r="D32" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$45</f>
+        <v>440332.522896826</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="129" t="s">
         <v>342</v>
       </c>
-      <c r="C16" s="54" t="s">
-        <v>343</v>
-      </c>
-      <c r="D16" s="54"/>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="58" t="s">
-        <v>344</v>
-      </c>
-      <c r="C17" s="54" t="s">
-        <v>345</v>
-      </c>
-      <c r="D17" s="54"/>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="113"/>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="53" t="s">
-        <v>346</v>
-      </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="114"/>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="54" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="115" t="n">
-        <f aca="false">'Budget P&amp;L'!$N$10</f>
-        <v>1299970.85714286</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="54" t="s">
-        <v>293</v>
-      </c>
-      <c r="C21" s="54"/>
-      <c r="D21" s="115" t="n">
-        <f aca="false">'Budget P&amp;L'!$N$21</f>
-        <v>601564.605</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="54" t="s">
-        <v>348</v>
-      </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="115" t="n">
-        <f aca="false">'Budget P&amp;L'!$N$22</f>
-        <v>698406.252142857</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="54" t="s">
-        <v>349</v>
-      </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="116" t="n">
-        <f aca="false">IF('Budget P&amp;L'!$N$10=0,0,'Budget P&amp;L'!$N$22/'Budget P&amp;L'!$N$10)</f>
-        <v>0.537247622364282</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="C24" s="54"/>
-      <c r="D24" s="115" t="n">
-        <f aca="false">'Budget P&amp;L'!$N$40</f>
-        <v>277415.465</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="54" t="s">
-        <v>351</v>
-      </c>
-      <c r="C25" s="54"/>
-      <c r="D25" s="115" t="n">
-        <f aca="false">'Budget P&amp;L'!$N$42</f>
-        <v>420990.787142857</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="54" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="54"/>
-      <c r="D26" s="116" t="n">
-        <f aca="false">IF('Budget P&amp;L'!$N$10=0,0,'Budget P&amp;L'!$N$42/'Budget P&amp;L'!$N$10)</f>
-        <v>0.323846326884691</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="54" t="s">
-        <v>353</v>
-      </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="115" t="n">
+      <c r="C33" s="129"/>
+      <c r="D33" s="137" t="n">
+        <f aca="false">'Forecast 2026'!$N$46</f>
+        <v>0.358231076221518</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="128" t="s">
+        <v>396</v>
+      </c>
+      <c r="C34" s="129"/>
+      <c r="D34" s="136" t="n">
+        <f aca="false">'Forecast 2026'!$N$57</f>
+        <v>303531.554980159</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="129" t="s">
+        <v>397</v>
+      </c>
+      <c r="C35" s="129"/>
+      <c r="D35" s="136" t="n">
         <f aca="false">Assumptions!$B$28</f>
         <v>184500</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="C28" s="54"/>
-      <c r="D28" s="117" t="n">
-        <f aca="false">'Monthly Capacity'!$N$28</f>
-        <v>8196.8</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="54" t="s">
-        <v>355</v>
-      </c>
-      <c r="C29" s="54"/>
-      <c r="D29" s="117" t="n">
+    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="129" t="s">
+        <v>398</v>
+      </c>
+      <c r="C36" s="129"/>
+      <c r="D36" s="137" t="n">
+        <f aca="false">Assumptions!$B$15</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="129" t="s">
+        <v>399</v>
+      </c>
+      <c r="C37" s="129"/>
+      <c r="D37" s="137" t="n">
+        <f aca="false">'Budget vs Actual'!$B$50</f>
+        <v>0.907254388640216</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="129" t="s">
+        <v>400</v>
+      </c>
+      <c r="C38" s="129"/>
+      <c r="D38" s="138" t="n">
         <f aca="false">'Monthly Capacity'!$N$11</f>
         <v>254</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="54"/>
-      <c r="C30" s="54"/>
-      <c r="D30" s="54"/>
-    </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="53" t="s">
-        <v>356</v>
-      </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="51"/>
-    </row>
-    <row r="32" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C32" s="119" t="s">
-        <v>358</v>
-      </c>
-      <c r="D32" s="119"/>
-    </row>
-    <row r="33" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C33" s="119" t="s">
-        <v>359</v>
-      </c>
-      <c r="D33" s="119"/>
-    </row>
-    <row r="34" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C34" s="119" t="s">
-        <v>360</v>
-      </c>
-      <c r="D34" s="119"/>
-    </row>
-    <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C35" s="119" t="s">
-        <v>361</v>
-      </c>
-      <c r="D35" s="119"/>
-    </row>
-    <row r="36" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="119" t="s">
-        <v>362</v>
-      </c>
-      <c r="D36" s="119"/>
-    </row>
-    <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C37" s="119" t="s">
-        <v>363</v>
-      </c>
-      <c r="D37" s="119"/>
-    </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C38" s="119" t="s">
-        <v>364</v>
-      </c>
-      <c r="D38" s="119"/>
-    </row>
-    <row r="39" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C39" s="119" t="s">
-        <v>365</v>
-      </c>
-      <c r="D39" s="119"/>
-    </row>
-    <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="118" t="s">
-        <v>357</v>
-      </c>
-      <c r="C40" s="119" t="s">
-        <v>366</v>
-      </c>
-      <c r="D40" s="119"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="54"/>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="54"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="54"/>
+    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="129"/>
+      <c r="C39" s="129"/>
+      <c r="D39" s="129"/>
+    </row>
+    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="124" t="s">
+        <v>401</v>
+      </c>
+      <c r="C40" s="125"/>
+      <c r="D40" s="125"/>
+    </row>
+    <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C41" s="140" t="s">
+        <v>403</v>
+      </c>
+      <c r="D41" s="140"/>
+    </row>
+    <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C42" s="140" t="s">
+        <v>404</v>
+      </c>
+      <c r="D42" s="140"/>
+    </row>
+    <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C43" s="140" t="s">
+        <v>405</v>
+      </c>
+      <c r="D43" s="140"/>
+    </row>
+    <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C44" s="140" t="s">
+        <v>406</v>
+      </c>
+      <c r="D44" s="140"/>
+    </row>
+    <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C45" s="140" t="s">
+        <v>407</v>
+      </c>
+      <c r="D45" s="140"/>
+    </row>
+    <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C46" s="140" t="s">
+        <v>408</v>
+      </c>
+      <c r="D46" s="140"/>
+    </row>
+    <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C47" s="140" t="s">
+        <v>409</v>
+      </c>
+      <c r="D47" s="140"/>
+    </row>
+    <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="139" t="s">
+        <v>402</v>
+      </c>
+      <c r="C48" s="140" t="s">
+        <v>410</v>
+      </c>
+      <c r="D48" s="140"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="129"/>
+      <c r="C49" s="129"/>
+      <c r="D49" s="129"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="129"/>
+      <c r="C50" s="129"/>
+      <c r="D50" s="129"/>
+    </row>
+    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="129"/>
+      <c r="C51" s="129"/>
+      <c r="D51" s="129"/>
+    </row>
+    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="129"/>
+      <c r="C52" s="129"/>
+      <c r="D52" s="129"/>
+    </row>
+    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="129"/>
+      <c r="C53" s="129"/>
+      <c r="D53" s="129"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="129"/>
+      <c r="C54" s="129"/>
+      <c r="D54" s="129"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="129"/>
+      <c r="C55" s="129"/>
+      <c r="D55" s="129"/>
+    </row>
+    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="129"/>
+      <c r="C56" s="129"/>
+      <c r="D56" s="129"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="129"/>
+      <c r="C57" s="129"/>
+      <c r="D57" s="129"/>
+    </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="129"/>
+      <c r="C58" s="129"/>
+      <c r="D58" s="129"/>
+    </row>
+    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="129"/>
+      <c r="C59" s="129"/>
+      <c r="D59" s="129"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="129"/>
+      <c r="C60" s="129"/>
+      <c r="D60" s="129"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Firm_Budget_Forecast_2026.xlsx
+++ b/Firm_Budget_Forecast_2026.xlsx
@@ -458,7 +458,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="492">
   <si>
     <t xml:space="preserve">Onyx Accounting Group, LLC</t>
   </si>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">Employee Social Security</t>
   </si>
   <si>
-    <t xml:space="preserve">Withheld from the owner's paycheck. The company pays a matching amount — shown in section 2.</t>
+    <t xml:space="preserve">Withheld from the owner's paycheck. The company separately pays a matching SS and Medicare amount plus FUTA and AZ SUTA — that is the employer tax line in section 2.</t>
   </si>
   <si>
     <t xml:space="preserve">Employee Medicare</t>
@@ -1772,16 +1772,22 @@
     <t xml:space="preserve">NET AFTER-TAX CASH TO OWNER</t>
   </si>
   <si>
+    <t xml:space="preserve">Income tax (federal + Arizona)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total tax less the FICA already withheld from payroll. This is what estimates must cover.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quarterly estimated payment</t>
   </si>
   <si>
-    <t xml:space="preserve">Income tax not covered by payroll withholding, spread over four quarters. Adjust for anything already withheld from salary.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distribution needed to cover the K-1 tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keep at least this much distributable so the owner is not funding firm tax personally.</t>
+    <t xml:space="preserve">Income tax spread over four quarters. Reduce it by any federal or state income tax already withheld from the owner's salary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribution to cover the tax on K-1 income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The K-1's pro-rata share of the income tax — the part the salary does not fund. Keep at least this much distributable so the owner is not paying firm tax out of pocket.</t>
   </si>
   <si>
     <t xml:space="preserve">HOW TO READ THIS</t>
@@ -11712,7 +11718,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:E81"/>
+  <dimension ref="B1:E82"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -12399,8 +12405,8 @@
         <v>428</v>
       </c>
       <c r="C73" s="57" t="n">
-        <f aca="false">MAX(0,(C64-C60-C61-C62))/4</f>
-        <v>25004.9833258709</v>
+        <f aca="false">C59+C63</f>
+        <v>100019.933303484</v>
       </c>
       <c r="E73" s="19" t="s">
         <v>429</v>
@@ -12411,32 +12417,36 @@
         <v>430</v>
       </c>
       <c r="C74" s="57" t="n">
-        <f aca="false">MAX(0,C64-C60-C61-C62)</f>
-        <v>100019.933303484</v>
+        <f aca="false">C73/4</f>
+        <v>25004.9833258709</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="69" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="49" t="s">
         <v>432</v>
       </c>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-    </row>
-    <row r="77" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B77" s="113" t="s">
+      <c r="C75" s="57" t="n">
+        <f aca="false">IF(C51=0,0,C73*C48/C51)</f>
+        <v>62786.1253072978</v>
+      </c>
+      <c r="E75" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="C77" s="113"/>
-      <c r="D77" s="113"/>
-      <c r="E77" s="113"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="69" t="s">
+        <v>434</v>
+      </c>
+      <c r="C77" s="51"/>
+      <c r="D77" s="51"/>
+      <c r="E77" s="51"/>
     </row>
     <row r="78" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="113" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C78" s="113"/>
       <c r="D78" s="113"/>
@@ -12444,7 +12454,7 @@
     </row>
     <row r="79" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="113" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C79" s="113"/>
       <c r="D79" s="113"/>
@@ -12452,7 +12462,7 @@
     </row>
     <row r="80" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="113" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C80" s="113"/>
       <c r="D80" s="113"/>
@@ -12460,19 +12470,27 @@
     </row>
     <row r="81" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="113" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C81" s="113"/>
       <c r="D81" s="113"/>
       <c r="E81" s="113"/>
     </row>
+    <row r="82" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="113" t="s">
+        <v>439</v>
+      </c>
+      <c r="C82" s="113"/>
+      <c r="D82" s="113"/>
+      <c r="E82" s="113"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
     <mergeCell ref="B79:E79"/>
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -12506,45 +12524,45 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="69" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C6" s="51"/>
       <c r="D6" s="51"/>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="124" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C7" s="125" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D7" s="125"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="52" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C8" s="125" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D8" s="125"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="52" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C9" s="125" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D9" s="125"/>
     </row>
@@ -12555,62 +12573,62 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="69" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C11" s="51"/>
       <c r="D11" s="51"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="52" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C12" s="125" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D12" s="125"/>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="52" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C13" s="125" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D13" s="125"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="52" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C14" s="125" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D14" s="125"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="52" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C15" s="125" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D15" s="125"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="52" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C16" s="125" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D16" s="125"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="52" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C17" s="125" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D17" s="125"/>
     </row>
@@ -12621,35 +12639,35 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="69" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C19" s="51"/>
       <c r="D19" s="127"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="128" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D20" s="126"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="124" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D21" s="129"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="52" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D22" s="126"/>
     </row>
@@ -12658,7 +12676,7 @@
         <v>302</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D23" s="126"/>
     </row>
@@ -12667,7 +12685,7 @@
         <v>303</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D24" s="129"/>
     </row>
@@ -12678,14 +12696,14 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="69" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="49" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="132" t="n">
@@ -12695,7 +12713,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="49" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C28" s="49"/>
       <c r="D28" s="132" t="n">
@@ -12705,7 +12723,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="49" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="132" t="n">
@@ -12715,7 +12733,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="49" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="132" t="n">
@@ -12725,7 +12743,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="52" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C31" s="49"/>
       <c r="D31" s="132" t="n">
@@ -12745,7 +12763,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="52" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C33" s="49"/>
       <c r="D33" s="132" t="n">
@@ -12755,7 +12773,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="49" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C34" s="49"/>
       <c r="D34" s="132" t="n">
@@ -12765,7 +12783,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="49" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C35" s="49"/>
       <c r="D35" s="133" t="n">
@@ -12775,7 +12793,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="49" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C36" s="49"/>
       <c r="D36" s="133" t="n">
@@ -12785,7 +12803,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="49" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C37" s="49"/>
       <c r="D37" s="134" t="n">
@@ -12800,80 +12818,80 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="69" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C39" s="51"/>
       <c r="D39" s="51"/>
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C40" s="136" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D40" s="136"/>
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C41" s="136" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D41" s="136"/>
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C42" s="136" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D42" s="136"/>
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C43" s="136" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D43" s="136"/>
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C44" s="136" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D44" s="136"/>
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C45" s="136" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D45" s="136"/>
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C46" s="136" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D46" s="136"/>
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="135" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C47" s="136" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D47" s="136"/>
     </row>
